--- a/tame_output/ON/bt/strategyON_20240330.xlsx
+++ b/tame_output/ON/bt/strategyON_20240330.xlsx
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-414.8%</t>
+          <t>-415.0%</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-169.1%</t>
+          <t>-169.2%</t>
         </is>
       </c>
     </row>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>70.5%</t>
+          <t>70.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>-9.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-410.8%</t>
+          <t>-408.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-182.0%</t>
+          <t>-182.1%</t>
         </is>
       </c>
     </row>
@@ -1395,7 +1395,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>49.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-112.4%</t>
+          <t>-112.5%</t>
         </is>
       </c>
     </row>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537429</v>
+        <v>3.27116857953743</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382194</v>
+        <v>3.272760131382195</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074625</v>
+        <v>3.251475576074626</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911641</v>
+        <v>3.233800325911643</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213498</v>
+        <v>3.2235393782135</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416047</v>
+        <v>3.23116753741605</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.23598197738233</v>
+        <v>3.235981977382333</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495501</v>
+        <v>3.278199702495504</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347058</v>
+        <v>3.299136146347061</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.28737757613002</v>
+        <v>3.287377576130023</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178246</v>
+        <v>3.31588437417825</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207815</v>
+        <v>3.305316798207819</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310984</v>
+        <v>3.284619513310988</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006536</v>
+        <v>3.30584953900654</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309426</v>
+        <v>3.31108639130943</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970907</v>
+        <v>3.304715716970911</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330525</v>
+        <v>3.300815818330528</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.30261819419174</v>
+        <v>3.302618194191743</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108642</v>
+        <v>3.305023265108645</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097824</v>
+        <v>3.341378723097826</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.37443904309412</v>
+        <v>3.374439043094122</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199289</v>
+        <v>3.405960511199291</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969598</v>
+        <v>3.4246333549696</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923091</v>
+        <v>3.419979433923093</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297753</v>
+        <v>3.458100091297755</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.44775050131762</v>
+        <v>3.447750501317621</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737174</v>
+        <v>3.503515506737175</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341317</v>
+        <v>3.503170282341318</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50044609677668</v>
+        <v>3.500446096776682</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407495</v>
+        <v>3.492445136407494</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199887</v>
+        <v>3.496848329199886</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.49996816391063</v>
+        <v>3.499968163910629</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078598</v>
+        <v>3.490055666078597</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880271</v>
+        <v>3.48587501888027</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234396</v>
+        <v>3.480688917234395</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860586</v>
+        <v>3.493712438860585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767399</v>
+        <v>3.492098065767398</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792544</v>
+        <v>3.573670449792543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628922</v>
+        <v>3.600034689628921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116218</v>
+        <v>3.710931958116217</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.83324917230973</v>
+        <v>3.833249172309729</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858732</v>
+        <v>3.839370871858731</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761809</v>
+        <v>3.787326853761808</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077645</v>
+        <v>3.692928280077646</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457902</v>
+        <v>3.770419008457904</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
@@ -45665,16 +45665,16 @@
         <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-2.532226997015693</v>
+        <v>-2.534369471592256</v>
       </c>
       <c r="E1918" t="n">
-        <v>2.071178518336229</v>
+        <v>2.070321528505604</v>
       </c>
       <c r="F1918" t="n">
-        <v>0.4204246025176531</v>
+        <v>0.4186747014689761</v>
       </c>
       <c r="G1918" t="n">
-        <v>3.336680502966845</v>
+        <v>3.335630562337639</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240330.xlsx
+++ b/tame_output/ON/bt/strategyON_20240330.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>59.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.9%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.5%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.8%</t>
+          <t>-15.5%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.5%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>34.7%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>58.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.9%</t>
+          <t>-5.0%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-68.5%</t>
+          <t>-70.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.4%</t>
+          <t>109.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.7%</t>
+          <t>125.7%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>92.3%</t>
+          <t>92.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-541.8%</t>
+          <t>-561.3%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-45.8%</t>
+          <t>-46.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-63.0%</t>
+          <t>-65.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.7%</t>
+          <t>90.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>498.7%</t>
+          <t>507.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-415.0%</t>
+          <t>-434.1%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>28.8%</t>
+          <t>26.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>60.8%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.1%</t>
+          <t>99.2%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-217.1%</t>
+          <t>-224.9%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-35.6%</t>
+          <t>-36.2%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,32 +1165,32 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>26.3%</t>
+          <t>23.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>43.7%</t>
+          <t>43.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-74.1%</t>
+          <t>-63.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-17.8%</t>
+          <t>-9.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-169.2%</t>
+          <t>-176.8%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-17.1%</t>
+          <t>-17.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>70.4%</t>
+          <t>70.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-283.3%</t>
+          <t>-287.3%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-30.4%</t>
+          <t>-30.7%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-9.1%</t>
+          <t>-10.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>56.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-408.9%</t>
+          <t>178.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-149.2%</t>
+          <t>-151.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-182.1%</t>
+          <t>-186.1%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>64.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>49.9%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>60.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.0%</t>
+          <t>96.1%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-170.4%</t>
+          <t>-172.8%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1471,17 +1471,17 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-26.2%</t>
+          <t>-26.4%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>61.3%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.1%</t>
+          <t>-15.2%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-112.5%</t>
+          <t>-114.8%</t>
         </is>
       </c>
     </row>
@@ -44055,16 +44055,16 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-0.4422140330987777</v>
+        <v>-0.6367036280647618</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.939704628996693</v>
+        <v>2.861908791010299</v>
       </c>
       <c r="F1848" t="n">
-        <v>1.393312858698349</v>
+        <v>1.352977623046232</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.952934381768961</v>
+        <v>3.92873324037769</v>
       </c>
     </row>
     <row r="1849">
@@ -44072,22 +44072,22 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382195</v>
+        <v>3.272760131382194</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-0.6502180914518549</v>
+        <v>-0.844707686417839</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.861395150209387</v>
+        <v>2.783599312222993</v>
       </c>
       <c r="F1849" t="n">
-        <v>1.393312858698349</v>
+        <v>1.352977623046232</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.957826526322886</v>
+        <v>3.933625384931616</v>
       </c>
     </row>
     <row r="1850">
@@ -44095,22 +44095,22 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074626</v>
+        <v>3.251475576074625</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-0.9206180541607403</v>
+        <v>-1.115107649126724</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.748316621463821</v>
+        <v>2.670520783477428</v>
       </c>
       <c r="F1850" t="n">
-        <v>1.122912895989464</v>
+        <v>1.082577660337347</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.790668005035543</v>
+        <v>3.766466863644273</v>
       </c>
     </row>
     <row r="1851">
@@ -44118,22 +44118,22 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911643</v>
+        <v>3.233800325911642</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.259776431749262</v>
+        <v>-1.454266026715246</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.605737569734861</v>
+        <v>2.527941731748468</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.783754518400942</v>
+        <v>0.7434192827488249</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.580257277788879</v>
+        <v>3.556056136397609</v>
       </c>
     </row>
     <row r="1852">
@@ -44141,22 +44141,22 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.2235393782135</v>
+        <v>3.223539378213498</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-1.587793653476741</v>
+        <v>-1.782283248442725</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.494868970782638</v>
+        <v>2.417073132796244</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.4557372966734629</v>
+        <v>0.4154020610213457</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.40378523449116</v>
+        <v>3.379584093099889</v>
       </c>
     </row>
     <row r="1853">
@@ -44164,22 +44164,22 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.23116753741605</v>
+        <v>3.231167537416048</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-1.58445690696777</v>
+        <v>-1.778946501933754</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.504302419794795</v>
+        <v>2.426506581808402</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.4584293290924942</v>
+        <v>0.4180940934403771</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.413499204351147</v>
+        <v>3.389298062959877</v>
       </c>
     </row>
     <row r="1854">
@@ -44187,22 +44187,22 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382333</v>
+        <v>3.235981977382331</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-1.951167958634316</v>
+        <v>-2.1456575536003</v>
       </c>
       <c r="E1854" t="n">
-        <v>2.358724391171909</v>
+        <v>2.280928553185515</v>
       </c>
       <c r="F1854" t="n">
-        <v>0.09171827742594862</v>
+        <v>0.05138304177383146</v>
       </c>
       <c r="G1854" t="n">
-        <v>3.194578965394952</v>
+        <v>3.170377824003682</v>
       </c>
     </row>
     <row r="1855">
@@ -44210,22 +44210,22 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495504</v>
+        <v>3.278199702495502</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-2.336348349564388</v>
+        <v>-2.530837944530372</v>
       </c>
       <c r="E1855" t="n">
-        <v>2.203194773612744</v>
+        <v>2.12539893562635</v>
       </c>
       <c r="F1855" t="n">
-        <v>0.09171827742594862</v>
+        <v>0.05138304177383146</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.193121504207815</v>
+        <v>3.168920362816545</v>
       </c>
     </row>
     <row r="1856">
@@ -44233,22 +44233,22 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347061</v>
+        <v>3.299136146347058</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-2.680031122791051</v>
+        <v>-2.874520717757035</v>
       </c>
       <c r="E1856" t="n">
-        <v>2.067490787776695</v>
+        <v>1.989694949790301</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.01618777460126958</v>
+        <v>-0.05652301025338674</v>
       </c>
       <c r="G1856" t="n">
-        <v>3.130146996446101</v>
+        <v>3.10594585505483</v>
       </c>
     </row>
     <row r="1857">
@@ -44256,22 +44256,22 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130023</v>
+        <v>3.287377576130021</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.037681473029399</v>
+        <v>-3.232171067995383</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.920536706337613</v>
+        <v>1.842740868351219</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.3738381248396177</v>
+        <v>-0.4141733604917349</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.911662844959349</v>
+        <v>2.887461703568079</v>
       </c>
     </row>
     <row r="1858">
@@ -44279,22 +44279,22 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.31588437417825</v>
+        <v>3.315884374178247</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-3.044342413251547</v>
+        <v>-3.238832008217531</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.919645256949013</v>
+        <v>1.84184941896262</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.3738381248396177</v>
+        <v>-0.4141733604917349</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.913435771659609</v>
+        <v>2.889234630268339</v>
       </c>
     </row>
     <row r="1859">
@@ -44302,22 +44302,22 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207819</v>
+        <v>3.305316798207816</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-3.476148206401334</v>
+        <v>-3.670637801367318</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.733255827156503</v>
+        <v>1.655459989170109</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.5102556212808846</v>
+        <v>-0.5505908569330018</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.817918161262253</v>
+        <v>2.793717019870983</v>
       </c>
     </row>
     <row r="1860">
@@ -44325,22 +44325,22 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310988</v>
+        <v>3.284619513310985</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-3.802580735269078</v>
+        <v>-3.997070330235062</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.590967590611496</v>
+        <v>1.513171752625103</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.5927238717880328</v>
+        <v>-0.6330591074401499</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.756721985960055</v>
+        <v>2.732520844568785</v>
       </c>
     </row>
     <row r="1861">
@@ -44348,22 +44348,22 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.30584953900654</v>
+        <v>3.305849539006536</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-3.804144886379381</v>
+        <v>-3.998634481345365</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.58892252182334</v>
+        <v>1.511126683836946</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.5927238717880328</v>
+        <v>-0.6330591074401499</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.75530257761602</v>
+        <v>2.73110143622475</v>
       </c>
     </row>
     <row r="1862">
@@ -44371,22 +44371,22 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.31108639130943</v>
+        <v>3.311086391309427</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-4.167771131279694</v>
+        <v>-4.362260726245678</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.449959584097456</v>
+        <v>1.372163746111063</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.6909455086551586</v>
+        <v>-0.7312807443072757</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.702857155729986</v>
+        <v>2.678656014338716</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970911</v>
+        <v>3.304715716970908</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-4.165344066750976</v>
+        <v>-4.35983366171696</v>
       </c>
       <c r="E1863" t="n">
-        <v>1.450184924914775</v>
+        <v>1.372389086928381</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.6912782904623102</v>
+        <v>-0.7316135261144274</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.701912001651527</v>
+        <v>2.677710860260257</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330528</v>
+        <v>3.300815818330526</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-4.573932843931654</v>
+        <v>-4.768422438897638</v>
       </c>
       <c r="E1864" t="n">
-        <v>1.285510958057263</v>
+        <v>1.207715120070869</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.099867067642989</v>
+        <v>-1.140202303295106</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.455520279357879</v>
+        <v>2.431319137966609</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191743</v>
+        <v>3.302618194191741</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-4.986915328072748</v>
+        <v>-5.181404923038731</v>
       </c>
       <c r="E1865" t="n">
-        <v>1.115503396872286</v>
+        <v>1.037707558885892</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.099867067642989</v>
+        <v>-1.140202303295106</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.45070571182934</v>
+        <v>2.426504570438069</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108645</v>
+        <v>3.305023265108643</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-5.403307202359746</v>
+        <v>-5.597796797325729</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.9469406977663639</v>
+        <v>0.8691448597799707</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.099867067642989</v>
+        <v>-1.140202303295106</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.448699762438217</v>
+        <v>2.424498621046947</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097826</v>
+        <v>3.341378723097825</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-5.77998421288959</v>
+        <v>-5.974473807855573</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.8065285842231051</v>
+        <v>0.7287327462367119</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.099867067642989</v>
+        <v>-1.140202303295106</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.458958453106896</v>
+        <v>2.434757311715626</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094122</v>
+        <v>3.374439043094121</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-5.793699077214701</v>
+        <v>-5.988188672180685</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.7971422036387561</v>
+        <v>0.7193463656523629</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.099867067642989</v>
+        <v>-1.140202303295106</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.455058018252591</v>
+        <v>2.430856876861321</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199291</v>
+        <v>3.40596051119929</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-6.106523876459681</v>
+        <v>-6.301013471425664</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.6704172039957652</v>
+        <v>0.592621366009372</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.099867067642989</v>
+        <v>-1.140202303295106</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.453462938307592</v>
+        <v>2.429261796916322</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.4246333549696</v>
+        <v>3.424633354969599</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-6.111336914925018</v>
+        <v>-6.305826509891001</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.6722709645388383</v>
+        <v>0.5944751265524451</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.101413702345774</v>
+        <v>-1.141748937997892</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.456313933415128</v>
+        <v>2.432112792023858</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923093</v>
+        <v>3.419979433923092</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-6.544686023035254</v>
+        <v>-6.739175618001237</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.4949050167603408</v>
+        <v>0.4171091787739476</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.101413702345774</v>
+        <v>-1.141748937997892</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.452287628880725</v>
+        <v>2.428086487489455</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297755</v>
+        <v>3.458100091297754</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-6.927687411777885</v>
+        <v>-7.122177006743868</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.3416023599417044</v>
+        <v>0.2638065219553112</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.101413702345774</v>
+        <v>-1.141748937997892</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.452185527559141</v>
+        <v>2.427984386167871</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.302672737949162</v>
+        <v>-7.497162332915146</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.1941797454446235</v>
+        <v>0.1163839074582302</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.476399028517052</v>
+        <v>-1.516734264169169</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.229765847827805</v>
+        <v>2.205564706436535</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-7.662203060453164</v>
+        <v>-7.856692655419147</v>
       </c>
       <c r="E1874" t="n">
-        <v>0.0557179197410731</v>
+        <v>-0.02207791824532013</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.476399028517052</v>
+        <v>-1.516734264169169</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.235116151125855</v>
+        <v>2.210915009734585</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-7.988603089118177</v>
+        <v>-8.18309268408416</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.06692607176775445</v>
+        <v>-0.1447219097541477</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.802799057182065</v>
+        <v>-1.843134292834182</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.047192153884025</v>
+        <v>2.022991012492755</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776682</v>
+        <v>3.500446096776681</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-7.982126942324618</v>
+        <v>-8.176616537290601</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.06129386242856194</v>
+        <v>-0.1390897004149552</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.796322910388505</v>
+        <v>-1.836658146040622</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.05411959258193</v>
+        <v>2.029918451190659</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407494</v>
+        <v>3.492445136407496</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-7.978436017368206</v>
+        <v>-8.17292561233419</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.0598174924459971</v>
+        <v>-0.1376133304323908</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.796322910388505</v>
+        <v>-1.836658146040622</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.05411959258193</v>
+        <v>2.029918451190659</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611697</v>
+        <v>3.502786823611698</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.182694192698069</v>
+        <v>-8.377183787664054</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.1360075654593</v>
+        <v>-0.2138034034456942</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.923961855002494</v>
+        <v>-1.964297090654611</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.983049422932178</v>
+        <v>1.958848281540909</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199886</v>
+        <v>3.496848329199888</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.343333219186434</v>
+        <v>-8.537822814152419</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.19578062157021</v>
+        <v>-0.2735764595566041</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.03869532800489</v>
+        <v>-2.079030563657007</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.918691893615177</v>
+        <v>1.894490752223907</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910629</v>
+        <v>3.499968163910631</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.269863387518985</v>
+        <v>-8.46435298248497</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.1510209874098094</v>
+        <v>-0.2288168253962031</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.965225496337441</v>
+        <v>-2.005560731989558</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.978145494109068</v>
+        <v>1.953944352717797</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078597</v>
+        <v>3.490055666078598</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.444987804905528</v>
+        <v>-8.639477399871513</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.2065155336169098</v>
+        <v>-0.2843113716033039</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.140349913723985</v>
+        <v>-2.180685149376102</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.887626064424658</v>
+        <v>1.863424923033388</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.48587501888027</v>
+        <v>3.485875018880272</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-8.679439898920018</v>
+        <v>-8.873929493886003</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.3075155361243018</v>
+        <v>-0.3853113741106955</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.140349913723985</v>
+        <v>-2.180685149376102</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.880406899523062</v>
+        <v>1.856205758131792</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234395</v>
+        <v>3.480688917234397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-8.967243743457256</v>
+        <v>-9.161733338423241</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.4293092647131735</v>
+        <v>-0.5071051026995672</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.428153758261223</v>
+        <v>-2.46848899391334</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.701052402026743</v>
+        <v>1.676851260635473</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860585</v>
+        <v>3.493712438860586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.197068190621081</v>
+        <v>-9.391557785587066</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.520123253740147</v>
+        <v>-0.5979190917265411</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.590801295331384</v>
+        <v>-2.631136530983501</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.604579669623203</v>
+        <v>1.580378528231933</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767398</v>
+        <v>3.4920980657674</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.429097110357343</v>
+        <v>-9.623586705323328</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.6102410930055373</v>
+        <v>-0.688036930991931</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.652813992519807</v>
+        <v>-2.693149228171924</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.570065779939264</v>
+        <v>1.545864638547993</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792543</v>
+        <v>3.573670449792544</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.37708159638853</v>
+        <v>-9.571571191354515</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.5854445517316109</v>
+        <v>-0.663240389718005</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.652813992519807</v>
+        <v>-2.693149228171924</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.574056115625664</v>
+        <v>1.549854974234394</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628921</v>
+        <v>3.600034689628923</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.51875343811265</v>
+        <v>-9.713243033078635</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.6435885153200007</v>
+        <v>-0.7213843533063948</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.652813992519807</v>
+        <v>-2.693149228171924</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.572580888726923</v>
+        <v>1.548379747335653</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410719</v>
+        <v>3.69156815841072</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.321484032384653</v>
+        <v>-9.515973627350638</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.5496273428639298</v>
+        <v>-0.6274231808503234</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.455544586791809</v>
+        <v>-2.495879822443926</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.705995942328594</v>
+        <v>1.681794800937324</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240578</v>
+        <v>3.676837974240579</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.122331925147554</v>
+        <v>-9.316821520113539</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.483017633615773</v>
+        <v>-0.5608134716021671</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.290222060841995</v>
+        <v>-2.330557296494113</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.792138324251799</v>
+        <v>1.767937182860529</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.896486772428144</v>
+        <v>-9.090976367394127</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.3831004994918001</v>
+        <v>-0.4608963374781934</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.248295385254832</v>
+        <v>-2.288630620906949</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.826873402640306</v>
+        <v>1.802672261249036</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282102</v>
+        <v>3.684840248282103</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.610211960105449</v>
+        <v>-8.804701555071432</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.2674514300066635</v>
+        <v>-0.3452472679930567</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.248295385254832</v>
+        <v>-2.288630620906949</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.828012547196365</v>
+        <v>1.803811405805094</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116217</v>
+        <v>3.710931958116218</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.383416133032116</v>
+        <v>-8.577905727998099</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.1740993250152223</v>
+        <v>-0.2518951630016155</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.180181440633287</v>
+        <v>-2.220516676285405</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.871514688131399</v>
+        <v>1.847313546740129</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.099507402103367</v>
+        <v>-8.29399699706935</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.05480212840508614</v>
+        <v>-0.1325979663914794</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.180181440633287</v>
+        <v>-2.220516676285405</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.877248392370036</v>
+        <v>1.853047250978765</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-7.852520151910414</v>
+        <v>-8.047009746876398</v>
       </c>
       <c r="E1894" t="n">
-        <v>0.03425550927822929</v>
+        <v>-0.04354032870816393</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.933194190440335</v>
+        <v>-1.973529426092453</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.015703480091942</v>
+        <v>1.991502338700672</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-7.588683284706345</v>
+        <v>-7.783172879672329</v>
       </c>
       <c r="E1895" t="n">
-        <v>0.1299067748469493</v>
+        <v>0.05211093686055568</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.933194190440335</v>
+        <v>-1.973529426092453</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.005819998779034</v>
+        <v>1.981618857387764</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-7.321441483837948</v>
+        <v>-7.515931078803932</v>
       </c>
       <c r="E1896" t="n">
-        <v>0.2349689346949346</v>
+        <v>0.157173096708541</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.933194190440335</v>
+        <v>-1.973529426092453</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.00398543827966</v>
+        <v>1.97978429688839</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-7.045632320437464</v>
+        <v>-7.240121915403448</v>
       </c>
       <c r="E1897" t="n">
-        <v>0.3449922850816671</v>
+        <v>0.2671964470952735</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.844174882161602</v>
+        <v>-1.884510117813719</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.057096708273439</v>
+        <v>2.03289556688217</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-6.776564732670485</v>
+        <v>-6.971054327636469</v>
       </c>
       <c r="E1898" t="n">
-        <v>0.4532878263339528</v>
+        <v>0.3754919883475591</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.575107294394622</v>
+        <v>-1.61544253004674</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.219205767079121</v>
+        <v>2.19500462568785</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-6.512504794347689</v>
+        <v>-6.706994389313673</v>
       </c>
       <c r="E1899" t="n">
-        <v>0.545651485501319</v>
+        <v>0.4678556475149254</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.311047356071826</v>
+        <v>-1.351382591723943</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.364381413911046</v>
+        <v>2.340180272519776</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309729</v>
+        <v>3.83324917230973</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-5.805425170842851</v>
+        <v>-5.999914765808835</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.8256963012429535</v>
+        <v>0.7479004632565598</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.311047356071826</v>
+        <v>-1.351382591723943</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.361594380250745</v>
+        <v>2.337393238859475</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858731</v>
+        <v>3.839370871858732</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-5.555784140856899</v>
+        <v>-5.750273735822883</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.9258963371251756</v>
+        <v>0.8481004991387819</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.061406326085875</v>
+        <v>-1.101741561737992</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.511722622130158</v>
+        <v>2.487521480738887</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-5.301242241515823</v>
+        <v>-5.495731836481808</v>
       </c>
       <c r="E1902" t="n">
-        <v>1.027079918082363</v>
+        <v>0.949284080095969</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.8068644267447991</v>
+        <v>-0.8471996623969162</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.66381458295556</v>
+        <v>2.63961344156429</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761808</v>
+        <v>3.787326853761809</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-5.067761019286224</v>
+        <v>-5.262250614252209</v>
       </c>
       <c r="E1903" t="n">
-        <v>1.128396835812055</v>
+        <v>1.050600997825661</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.5733832045152005</v>
+        <v>-0.6137184401673177</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.811827745131172</v>
+        <v>2.787626603739901</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-4.888052489142352</v>
+        <v>-5.082542084108336</v>
       </c>
       <c r="E1904" t="n">
-        <v>1.197388037556645</v>
+        <v>1.11959219957025</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.5162117003525044</v>
+        <v>-0.5565469360046216</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.84323843731583</v>
+        <v>2.81903729592456</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-4.755777015511465</v>
+        <v>-4.95026661047745</v>
       </c>
       <c r="E1905" t="n">
-        <v>1.245665713756026</v>
+        <v>1.167869875769632</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.3839362267216178</v>
+        <v>-0.4242714623737349</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.917971208241389</v>
+        <v>2.893770066850119</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-4.565177340838313</v>
+        <v>-4.759666935804297</v>
       </c>
       <c r="E1906" t="n">
-        <v>1.324720644312924</v>
+        <v>1.24692480632653</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.1933365520484649</v>
+        <v>-0.2336717877005821</v>
       </c>
       <c r="G1906" t="n">
-        <v>3.035146073732918</v>
+        <v>3.010944932341647</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-4.316177542154731</v>
+        <v>-4.510667137120716</v>
       </c>
       <c r="E1907" t="n">
-        <v>1.437226905010015</v>
+        <v>1.359431067023621</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.1933365520484649</v>
+        <v>-0.2336717877005821</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.048052414956576</v>
+        <v>3.023851273565306</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077646</v>
+        <v>3.692928280077645</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-4.421767531927836</v>
+        <v>-4.616257126893821</v>
       </c>
       <c r="E1908" t="n">
-        <v>1.267014979501555</v>
+        <v>1.189219141515161</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.2989265418215692</v>
+        <v>-0.3392617774736864</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.856722491493495</v>
+        <v>2.832521350102225</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457904</v>
+        <v>3.770419008457901</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-4.142740236272209</v>
+        <v>-4.337229831238194</v>
       </c>
       <c r="E1909" t="n">
-        <v>1.427170239640892</v>
+        <v>1.349374401654498</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.2989265418215692</v>
+        <v>-0.3392617774736864</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.905266833370582</v>
+        <v>2.881065691979311</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.76033011118081</v>
+        <v>3.760330111180809</v>
       </c>
       <c r="C1910" t="n">
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-3.866002061601396</v>
+        <v>-4.060491656567381</v>
       </c>
       <c r="E1910" t="n">
-        <v>1.541244521495212</v>
+        <v>1.463448683508818</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.1171098807116435</v>
+        <v>-0.1574451163637606</v>
       </c>
       <c r="G1910" t="n">
-        <v>3.017735842022531</v>
+        <v>2.993534700631261</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-3.739109655166327</v>
+        <v>-3.933599250132311</v>
       </c>
       <c r="E1911" t="n">
-        <v>1.583287497815761</v>
+        <v>1.505491659829368</v>
       </c>
       <c r="F1911" t="n">
-        <v>0.009782525723426472</v>
+        <v>-0.03055270992869069</v>
       </c>
       <c r="G1911" t="n">
-        <v>3.085157299630095</v>
+        <v>3.060956158238825</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-3.5515221472564</v>
+        <v>-3.746011742222384</v>
       </c>
       <c r="E1912" t="n">
-        <v>1.651361888884639</v>
+        <v>1.573566050898245</v>
       </c>
       <c r="F1912" t="n">
-        <v>0.009782525723426472</v>
+        <v>-0.03055270992869069</v>
       </c>
       <c r="G1912" t="n">
-        <v>3.078196687535002</v>
+        <v>3.053995546143732</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-3.309373753802542</v>
+        <v>-3.503863348768526</v>
       </c>
       <c r="E1913" t="n">
-        <v>1.762683600647325</v>
+        <v>1.684887762660931</v>
       </c>
       <c r="F1913" t="n">
-        <v>0.009782525723426472</v>
+        <v>-0.03055270992869069</v>
       </c>
       <c r="G1913" t="n">
-        <v>3.092659041916145</v>
+        <v>3.068457900524875</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-3.246144382034193</v>
+        <v>-3.440633977000178</v>
       </c>
       <c r="E1914" t="n">
-        <v>1.782507469813859</v>
+        <v>1.704711631827466</v>
       </c>
       <c r="F1914" t="n">
-        <v>0.009782525723426472</v>
+        <v>-0.03055270992869069</v>
       </c>
       <c r="G1914" t="n">
-        <v>3.08719116237534</v>
+        <v>3.06299002098407</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-3.059656689657187</v>
+        <v>-3.254146284623172</v>
       </c>
       <c r="E1915" t="n">
-        <v>1.854600640775239</v>
+        <v>1.776804802788845</v>
       </c>
       <c r="F1915" t="n">
-        <v>0.1962702181004327</v>
+        <v>0.1559349824483156</v>
       </c>
       <c r="G1915" t="n">
-        <v>3.196581871812121</v>
+        <v>3.17238073042085</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-3.038507490753743</v>
+        <v>-3.232997085719728</v>
       </c>
       <c r="E1916" t="n">
-        <v>1.870761298573942</v>
+        <v>1.792965460587548</v>
       </c>
       <c r="F1916" t="n">
-        <v>0.2174194170038761</v>
+        <v>0.1770841813517589</v>
       </c>
       <c r="G1916" t="n">
-        <v>3.216972369391513</v>
+        <v>3.192771228000242</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-2.794742048770299</v>
+        <v>-2.989231643736284</v>
       </c>
       <c r="E1917" t="n">
-        <v>1.96404818371437</v>
+        <v>1.886252345727977</v>
       </c>
       <c r="F1917" t="n">
-        <v>0.2174194170038761</v>
+        <v>0.1770841813517589</v>
       </c>
       <c r="G1917" t="n">
-        <v>3.212753077738563</v>
+        <v>3.188551936347293</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.385635162556305</v>
+        <v>3.627896148301777</v>
       </c>
       <c r="C1918" t="n">
         <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-2.534369471592256</v>
+        <v>-2.725203576543024</v>
       </c>
       <c r="E1918" t="n">
-        <v>2.070321528505604</v>
+        <v>1.993987886525296</v>
       </c>
       <c r="F1918" t="n">
-        <v>0.4186747014689761</v>
+        <v>0.3789495801677125</v>
       </c>
       <c r="G1918" t="n">
-        <v>3.335630562337639</v>
+        <v>3.311795489556881</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240330.xlsx
+++ b/tame_output/ON/bt/strategyON_20240330.xlsx
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382194</v>
+        <v>3.272760131382195</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074625</v>
+        <v>3.251475576074626</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911642</v>
+        <v>3.233800325911643</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213498</v>
+        <v>3.2235393782135</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416048</v>
+        <v>3.23116753741605</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382331</v>
+        <v>3.235981977382333</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495502</v>
+        <v>3.278199702495504</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347058</v>
+        <v>3.299136146347061</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130021</v>
+        <v>3.287377576130023</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178247</v>
+        <v>3.31588437417825</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207816</v>
+        <v>3.305316798207819</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310985</v>
+        <v>3.284619513310988</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006536</v>
+        <v>3.30584953900654</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309427</v>
+        <v>3.31108639130943</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970908</v>
+        <v>3.304715716970911</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330526</v>
+        <v>3.300815818330528</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191741</v>
+        <v>3.302618194191743</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108643</v>
+        <v>3.305023265108645</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097825</v>
+        <v>3.341378723097826</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094121</v>
+        <v>3.374439043094122</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.40596051119929</v>
+        <v>3.405960511199291</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969599</v>
+        <v>3.4246333549696</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923092</v>
+        <v>3.419979433923093</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297754</v>
+        <v>3.458100091297755</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776681</v>
+        <v>3.500446096776682</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407496</v>
+        <v>3.492445136407494</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611698</v>
+        <v>3.502786823611697</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199888</v>
+        <v>3.496848329199886</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910631</v>
+        <v>3.499968163910629</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078598</v>
+        <v>3.490055666078597</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880272</v>
+        <v>3.48587501888027</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234397</v>
+        <v>3.480688917234395</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860586</v>
+        <v>3.493712438860585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.4920980657674</v>
+        <v>3.492098065767398</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792544</v>
+        <v>3.573670449792543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628923</v>
+        <v>3.600034689628921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.69156815841072</v>
+        <v>3.691568158410719</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240579</v>
+        <v>3.676837974240578</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282103</v>
+        <v>3.684840248282102</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116218</v>
+        <v>3.710931958116217</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.83324917230973</v>
+        <v>3.833249172309729</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858732</v>
+        <v>3.839370871858731</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761809</v>
+        <v>3.787326853761808</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077645</v>
+        <v>3.692928280077646</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457901</v>
+        <v>3.770419008457904</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180809</v>
+        <v>3.76033011118081</v>
       </c>
       <c r="C1910" t="n">
         <v>3.088001770449517</v>

--- a/tame_output/ON/bt/strategyON_20240330.xlsx
+++ b/tame_output/ON/bt/strategyON_20240330.xlsx
@@ -605,12 +605,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1915</v>
+        <v>1916</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,17 +628,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-03-29</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>36.1%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>72.5%</t>
+          <t>68.6%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>29.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1915</v>
+        <v>1916</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-03-29</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>31.7%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,25 +801,25 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2021-03-21</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2021-03-24</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-11.3%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>58.4%</t>
+          <t>54.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.0%</t>
+          <t>-4.6%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-14.4%</t>
         </is>
       </c>
     </row>
@@ -916,26 +916,26 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-70.2%</t>
+          <t>-71.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.5%</t>
+          <t>108.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1915</v>
+        <v>1916</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,17 +944,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-03-29</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>125.7%</t>
+          <t>125.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>92.4%</t>
+          <t>91.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -973,11 +973,11 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-561.3%</t>
+          <t>-561.5%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>25.3%</t>
+          <t>24.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-65.0%</t>
+          <t>-66.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.8%</t>
+          <t>90.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>507.9%</t>
+          <t>507.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-434.1%</t>
+          <t>-460.9%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>26.6%</t>
+          <t>24.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1915</v>
+        <v>1916</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-03-29</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1131,11 +1131,11 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-224.9%</t>
+          <t>-225.0%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>23.0%</t>
+          <t>20.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>43.9%</t>
+          <t>43.7%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-63.6%</t>
+          <t>-62.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-9.7%</t>
+          <t>-9.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-176.8%</t>
+          <t>-187.5%</t>
         </is>
       </c>
     </row>
@@ -1232,26 +1232,26 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-17.8%</t>
+          <t>-20.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1915</v>
+        <v>1916</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,17 +1260,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-03-29</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>70.5%</t>
+          <t>68.9%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1289,11 +1289,11 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-287.3%</t>
+          <t>-287.1%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-10.1%</t>
+          <t>-13.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.5%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>178.7%</t>
+          <t>112.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-151.2%</t>
+          <t>-151.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-186.1%</t>
+          <t>-206.2%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>50.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1915</v>
+        <v>1916</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,17 +1418,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-03-29</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60.1%</t>
+          <t>62.0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.8%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,11 +1447,11 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-172.8%</t>
+          <t>-172.7%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>42.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.2%</t>
+          <t>-14.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-114.8%</t>
+          <t>-149.5%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1918"/>
+  <dimension ref="A1:G1919"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44055,16 +44055,16 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-0.6367036280647618</v>
+        <v>-0.6391093674693338</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.861908791010299</v>
+        <v>2.86094649524847</v>
       </c>
       <c r="F1848" t="n">
-        <v>1.352977623046232</v>
+        <v>1.35500359378675</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.92873324037769</v>
+        <v>3.929948822822001</v>
       </c>
     </row>
     <row r="1849">
@@ -44078,16 +44078,16 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-0.844707686417839</v>
+        <v>-0.847113425822411</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.783599312222993</v>
+        <v>2.782637016461165</v>
       </c>
       <c r="F1849" t="n">
-        <v>1.352977623046232</v>
+        <v>1.35500359378675</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.933625384931616</v>
+        <v>3.934840967375926</v>
       </c>
     </row>
     <row r="1850">
@@ -44101,16 +44101,16 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.115107649126724</v>
+        <v>-1.117513388531296</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.670520783477428</v>
+        <v>2.669558487715599</v>
       </c>
       <c r="F1850" t="n">
-        <v>1.082577660337347</v>
+        <v>1.084603631077864</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.766466863644273</v>
+        <v>3.767682446088583</v>
       </c>
     </row>
     <row r="1851">
@@ -44124,16 +44124,16 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.454266026715246</v>
+        <v>-1.456671766119819</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.527941731748468</v>
+        <v>2.526979435986639</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.7434192827488249</v>
+        <v>0.7454452534893421</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.556056136397609</v>
+        <v>3.557271718841919</v>
       </c>
     </row>
     <row r="1852">
@@ -44147,16 +44147,16 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-1.782283248442725</v>
+        <v>-1.784688987847298</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.417073132796244</v>
+        <v>2.416110837034416</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.4154020610213457</v>
+        <v>0.4174280317618629</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.379584093099889</v>
+        <v>3.3807996755442</v>
       </c>
     </row>
     <row r="1853">
@@ -44170,16 +44170,16 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-1.778946501933754</v>
+        <v>-1.781352241338326</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.426506581808402</v>
+        <v>2.425544286046573</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.4180940934403771</v>
+        <v>0.4201200641808943</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.389298062959877</v>
+        <v>3.390513645404187</v>
       </c>
     </row>
     <row r="1854">
@@ -44193,16 +44193,16 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-2.1456575536003</v>
+        <v>-2.148063293004872</v>
       </c>
       <c r="E1854" t="n">
-        <v>2.280928553185515</v>
+        <v>2.279966257423687</v>
       </c>
       <c r="F1854" t="n">
-        <v>0.05138304177383146</v>
+        <v>0.05340901251434871</v>
       </c>
       <c r="G1854" t="n">
-        <v>3.170377824003682</v>
+        <v>3.171593406447992</v>
       </c>
     </row>
     <row r="1855">
@@ -44216,16 +44216,16 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-2.530837944530372</v>
+        <v>-2.533243683934944</v>
       </c>
       <c r="E1855" t="n">
-        <v>2.12539893562635</v>
+        <v>2.124436639864521</v>
       </c>
       <c r="F1855" t="n">
-        <v>0.05138304177383146</v>
+        <v>0.05340901251434871</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.168920362816545</v>
+        <v>3.170135945260856</v>
       </c>
     </row>
     <row r="1856">
@@ -44239,16 +44239,16 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-2.874520717757035</v>
+        <v>-2.876926457161607</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.989694949790301</v>
+        <v>1.988732654028472</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.05652301025338674</v>
+        <v>-0.05449703951286949</v>
       </c>
       <c r="G1856" t="n">
-        <v>3.10594585505483</v>
+        <v>3.107161437499141</v>
       </c>
     </row>
     <row r="1857">
@@ -44262,16 +44262,16 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.232171067995383</v>
+        <v>-3.234576807399955</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.842740868351219</v>
+        <v>1.84177857258939</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.4141733604917349</v>
+        <v>-0.4121473897512176</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.887461703568079</v>
+        <v>2.88867728601239</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-3.238832008217531</v>
+        <v>-3.241237747622103</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.84184941896262</v>
+        <v>1.840887123200791</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.4141733604917349</v>
+        <v>-0.4121473897512176</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.889234630268339</v>
+        <v>2.890450212712649</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-3.670637801367318</v>
+        <v>-3.673043540771891</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.655459989170109</v>
+        <v>1.65449769340828</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.5505908569330018</v>
+        <v>-0.5485648861924846</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.793717019870983</v>
+        <v>2.794932602315293</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-3.997070330235062</v>
+        <v>-3.999476069639634</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.513171752625103</v>
+        <v>1.512209456863273</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.6330591074401499</v>
+        <v>-0.6310331366996327</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.732520844568785</v>
+        <v>2.733736427013095</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-3.998634481345365</v>
+        <v>-4.001040220749937</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.511126683836946</v>
+        <v>1.510164388075117</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.6330591074401499</v>
+        <v>-0.6310331366996327</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.73110143622475</v>
+        <v>2.73231701866906</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-4.362260726245678</v>
+        <v>-4.364666465650251</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.372163746111063</v>
+        <v>1.371201450349234</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.7312807443072757</v>
+        <v>-0.7292547735667585</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.678656014338716</v>
+        <v>2.679871596783026</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-4.35983366171696</v>
+        <v>-4.362239401121532</v>
       </c>
       <c r="E1863" t="n">
-        <v>1.372389086928381</v>
+        <v>1.371426791166553</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.7316135261144274</v>
+        <v>-0.7295875553739102</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.677710860260257</v>
+        <v>2.678926442704567</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-4.768422438897638</v>
+        <v>-4.77082817830221</v>
       </c>
       <c r="E1864" t="n">
-        <v>1.207715120070869</v>
+        <v>1.20675282430904</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.140202303295106</v>
+        <v>-1.138176332554589</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.431319137966609</v>
+        <v>2.432534720410919</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-5.181404923038731</v>
+        <v>-5.183810662443304</v>
       </c>
       <c r="E1865" t="n">
-        <v>1.037707558885892</v>
+        <v>1.036745263124063</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.140202303295106</v>
+        <v>-1.138176332554589</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.426504570438069</v>
+        <v>2.42772015288238</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-5.597796797325729</v>
+        <v>-5.600202536730301</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.8691448597799707</v>
+        <v>0.868182564018142</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.140202303295106</v>
+        <v>-1.138176332554589</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.424498621046947</v>
+        <v>2.425714203491257</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-5.974473807855573</v>
+        <v>-5.976879547260146</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.7287327462367119</v>
+        <v>0.7277704504748832</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.140202303295106</v>
+        <v>-1.138176332554589</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.434757311715626</v>
+        <v>2.435972894159936</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-5.988188672180685</v>
+        <v>-5.990594411585257</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.7193463656523629</v>
+        <v>0.7183840698905337</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.140202303295106</v>
+        <v>-1.138176332554589</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.430856876861321</v>
+        <v>2.432072459305631</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-6.301013471425664</v>
+        <v>-6.303419210830237</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.592621366009372</v>
+        <v>0.5916590702475428</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.140202303295106</v>
+        <v>-1.138176332554589</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.429261796916322</v>
+        <v>2.430477379360632</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-6.305826509891001</v>
+        <v>-6.308232249295574</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.5944751265524451</v>
+        <v>0.5935128307906159</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.141748937997892</v>
+        <v>-1.139722967257375</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.432112792023858</v>
+        <v>2.433328374468168</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-6.739175618001237</v>
+        <v>-6.74158135740581</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.4171091787739476</v>
+        <v>0.4161468830121184</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.141748937997892</v>
+        <v>-1.139722967257375</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.428086487489455</v>
+        <v>2.429302069933765</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.122177006743868</v>
+        <v>-7.124582746148441</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.2638065219553112</v>
+        <v>0.262844226193482</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.141748937997892</v>
+        <v>-1.139722967257375</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.427984386167871</v>
+        <v>2.429199968612181</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.497162332915146</v>
+        <v>-7.499568072319718</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.1163839074582302</v>
+        <v>0.1154216116964011</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.516734264169169</v>
+        <v>-1.514708293428652</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.205564706436535</v>
+        <v>2.206780288880845</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-7.856692655419147</v>
+        <v>-7.85909839482372</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.02207791824532013</v>
+        <v>-0.02304021400714928</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.516734264169169</v>
+        <v>-1.514708293428652</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.210915009734585</v>
+        <v>2.212130592178895</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.18309268408416</v>
+        <v>-8.185498423488733</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.1447219097541477</v>
+        <v>-0.1456842055159768</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.843134292834182</v>
+        <v>-1.841108322093665</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.022991012492755</v>
+        <v>2.024206594937065</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.176616537290601</v>
+        <v>-8.179022276695173</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.1390897004149552</v>
+        <v>-0.1400519961767843</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.836658146040622</v>
+        <v>-1.834632175300105</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.029918451190659</v>
+        <v>2.03113403363497</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.17292561233419</v>
+        <v>-8.175331351738762</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.1376133304323908</v>
+        <v>-0.1385756261942199</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.836658146040622</v>
+        <v>-1.834632175300105</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.029918451190659</v>
+        <v>2.03113403363497</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.377183787664054</v>
+        <v>-8.379589527068626</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.2138034034456942</v>
+        <v>-0.2147656992075229</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.964297090654611</v>
+        <v>-1.962271119914094</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.958848281540909</v>
+        <v>1.960063863985218</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.537822814152419</v>
+        <v>-8.540228553556991</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.2735764595566041</v>
+        <v>-0.2745387553184329</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.079030563657007</v>
+        <v>-2.07700459291649</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.894490752223907</v>
+        <v>1.895706334668217</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.46435298248497</v>
+        <v>-8.466758721889542</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.2288168253962031</v>
+        <v>-0.2297791211580322</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.005560731989558</v>
+        <v>-2.003534761249041</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.953944352717797</v>
+        <v>1.955159935162108</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.639477399871513</v>
+        <v>-8.641883139276086</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.2843113716033039</v>
+        <v>-0.285273667365133</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.180685149376102</v>
+        <v>-2.178659178635585</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.863424923033388</v>
+        <v>1.864640505477698</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-8.873929493886003</v>
+        <v>-8.876335233290575</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.3853113741106955</v>
+        <v>-0.3862736698725246</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.180685149376102</v>
+        <v>-2.178659178635585</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.856205758131792</v>
+        <v>1.857421340576102</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.161733338423241</v>
+        <v>-9.164139077827814</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.5071051026995672</v>
+        <v>-0.5080673984613964</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.46848899391334</v>
+        <v>-2.466463023172823</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.676851260635473</v>
+        <v>1.678066843079783</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.391557785587066</v>
+        <v>-9.393963524991639</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.5979190917265411</v>
+        <v>-0.5988813874883698</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.631136530983501</v>
+        <v>-2.629110560242984</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.580378528231933</v>
+        <v>1.581594110676243</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.623586705323328</v>
+        <v>-9.625992444727901</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.688036930991931</v>
+        <v>-0.6889992267537601</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.693149228171924</v>
+        <v>-2.691123257431407</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.545864638547993</v>
+        <v>1.547080220992304</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.571571191354515</v>
+        <v>-9.573976930759088</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.663240389718005</v>
+        <v>-0.6642026854798342</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.693149228171924</v>
+        <v>-2.691123257431407</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.549854974234394</v>
+        <v>1.551070556678704</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.713243033078635</v>
+        <v>-9.715648772483208</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.7213843533063948</v>
+        <v>-0.722346649068224</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.693149228171924</v>
+        <v>-2.691123257431407</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.548379747335653</v>
+        <v>1.549595329779963</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.515973627350638</v>
+        <v>-9.518379366755211</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.6274231808503234</v>
+        <v>-0.6283854766121526</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.495879822443926</v>
+        <v>-2.493853851703409</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.681794800937324</v>
+        <v>1.683010383381634</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.316821520113539</v>
+        <v>-9.319227259518112</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.5608134716021671</v>
+        <v>-0.5617757673639958</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.330557296494113</v>
+        <v>-2.328531325753596</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.767937182860529</v>
+        <v>1.769152765304839</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-9.090976367394127</v>
+        <v>-9.0933821067987</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.4608963374781934</v>
+        <v>-0.4618586332400225</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.288630620906949</v>
+        <v>-2.286604650166432</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.802672261249036</v>
+        <v>1.803887843693346</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.804701555071432</v>
+        <v>-8.807107294476005</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.3452472679930567</v>
+        <v>-0.3462095637548859</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.288630620906949</v>
+        <v>-2.286604650166432</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.803811405805094</v>
+        <v>1.805026988249405</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.577905727998099</v>
+        <v>-8.580311467402671</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.2518951630016155</v>
+        <v>-0.2528574587634447</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.220516676285405</v>
+        <v>-2.218490705544887</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.847313546740129</v>
+        <v>1.848529129184439</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.29399699706935</v>
+        <v>-8.296402736473922</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.1325979663914794</v>
+        <v>-0.1335602621533085</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.220516676285405</v>
+        <v>-2.218490705544887</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.853047250978765</v>
+        <v>1.854262833423076</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.047009746876398</v>
+        <v>-8.049415486280971</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.04354032870816393</v>
+        <v>-0.04450262446999309</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.973529426092453</v>
+        <v>-1.971503455351935</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.991502338700672</v>
+        <v>1.992717921144981</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-7.783172879672329</v>
+        <v>-7.785578619076902</v>
       </c>
       <c r="E1895" t="n">
-        <v>0.05211093686055568</v>
+        <v>0.05114864109872697</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.973529426092453</v>
+        <v>-1.971503455351935</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.981618857387764</v>
+        <v>1.982834439832074</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-7.515931078803932</v>
+        <v>-7.518336818208505</v>
       </c>
       <c r="E1896" t="n">
-        <v>0.157173096708541</v>
+        <v>0.1562108009467118</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.973529426092453</v>
+        <v>-1.971503455351935</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.97978429688839</v>
+        <v>1.9809998793327</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-7.240121915403448</v>
+        <v>-7.242527654808021</v>
       </c>
       <c r="E1897" t="n">
-        <v>0.2671964470952735</v>
+        <v>0.2662341513334447</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.884510117813719</v>
+        <v>-1.882484147073202</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.03289556688217</v>
+        <v>2.034111149326479</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-6.971054327636469</v>
+        <v>-6.973460067041041</v>
       </c>
       <c r="E1898" t="n">
-        <v>0.3754919883475591</v>
+        <v>0.37452969258573</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.61544253004674</v>
+        <v>-1.613416559306223</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.19500462568785</v>
+        <v>2.196220208132161</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-6.706994389313673</v>
+        <v>-6.709400128718245</v>
       </c>
       <c r="E1899" t="n">
-        <v>0.4678556475149254</v>
+        <v>0.4668933517530962</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.351382591723943</v>
+        <v>-1.349356620983426</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.340180272519776</v>
+        <v>2.341395854964086</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-5.999914765808835</v>
+        <v>-6.002320505213407</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.7479004632565598</v>
+        <v>0.7469381674947306</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.351382591723943</v>
+        <v>-1.349356620983426</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.337393238859475</v>
+        <v>2.338608821303785</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-5.750273735822883</v>
+        <v>-5.752679475227455</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.8481004991387819</v>
+        <v>0.8471382033769528</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.101741561737992</v>
+        <v>-1.099715590997475</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.487521480738887</v>
+        <v>2.488737063183198</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-5.495731836481808</v>
+        <v>-5.49813757588638</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.949284080095969</v>
+        <v>0.9483217843341398</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.8471996623969162</v>
+        <v>-0.8451736916563992</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.63961344156429</v>
+        <v>2.6408290240086</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-5.262250614252209</v>
+        <v>-5.264656353656782</v>
       </c>
       <c r="E1903" t="n">
-        <v>1.050600997825661</v>
+        <v>1.049638702063832</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.6137184401673177</v>
+        <v>-0.6116924694268007</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.787626603739901</v>
+        <v>2.788842186184211</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-5.082542084108336</v>
+        <v>-5.084947823512909</v>
       </c>
       <c r="E1904" t="n">
-        <v>1.11959219957025</v>
+        <v>1.118629903808422</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.5565469360046216</v>
+        <v>-0.5545209652641045</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.81903729592456</v>
+        <v>2.82025287836887</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-4.95026661047745</v>
+        <v>-4.952672349882023</v>
       </c>
       <c r="E1905" t="n">
-        <v>1.167869875769632</v>
+        <v>1.166907580007803</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.4242714623737349</v>
+        <v>-0.4222454916332179</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.893770066850119</v>
+        <v>2.894985649294429</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-4.759666935804297</v>
+        <v>-4.76207267520887</v>
       </c>
       <c r="E1906" t="n">
-        <v>1.24692480632653</v>
+        <v>1.245962510564701</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.2336717877005821</v>
+        <v>-0.231645816960065</v>
       </c>
       <c r="G1906" t="n">
-        <v>3.010944932341647</v>
+        <v>3.012160514785958</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-4.510667137120716</v>
+        <v>-4.513072876525289</v>
       </c>
       <c r="E1907" t="n">
-        <v>1.359431067023621</v>
+        <v>1.358468771261792</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.2336717877005821</v>
+        <v>-0.231645816960065</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.023851273565306</v>
+        <v>3.025066856009616</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-4.616257126893821</v>
+        <v>-4.618662866298394</v>
       </c>
       <c r="E1908" t="n">
-        <v>1.189219141515161</v>
+        <v>1.188256845753332</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.3392617774736864</v>
+        <v>-0.3372358067331694</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.832521350102225</v>
+        <v>2.833736932546535</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-4.337229831238194</v>
+        <v>-4.339635570642766</v>
       </c>
       <c r="E1909" t="n">
-        <v>1.349374401654498</v>
+        <v>1.348412105892669</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.3392617774736864</v>
+        <v>-0.3372358067331694</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.881065691979311</v>
+        <v>2.882281274423621</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-4.060491656567381</v>
+        <v>-4.062897395971953</v>
       </c>
       <c r="E1910" t="n">
-        <v>1.463448683508818</v>
+        <v>1.462486387746989</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.1574451163637606</v>
+        <v>-0.1554191456232436</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.993534700631261</v>
+        <v>2.994750283075571</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-3.933599250132311</v>
+        <v>-3.936004989536884</v>
       </c>
       <c r="E1911" t="n">
-        <v>1.505491659829368</v>
+        <v>1.504529364067538</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.03055270992869069</v>
+        <v>-0.02852673918817367</v>
       </c>
       <c r="G1911" t="n">
-        <v>3.060956158238825</v>
+        <v>3.062171740683135</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-3.746011742222384</v>
+        <v>-3.748417481626957</v>
       </c>
       <c r="E1912" t="n">
-        <v>1.573566050898245</v>
+        <v>1.572603755136416</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.03055270992869069</v>
+        <v>-0.02852673918817367</v>
       </c>
       <c r="G1912" t="n">
-        <v>3.053995546143732</v>
+        <v>3.055211128588042</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-3.503863348768526</v>
+        <v>-3.506269088173099</v>
       </c>
       <c r="E1913" t="n">
-        <v>1.684887762660931</v>
+        <v>1.683925466899102</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.03055270992869069</v>
+        <v>-0.02852673918817367</v>
       </c>
       <c r="G1913" t="n">
-        <v>3.068457900524875</v>
+        <v>3.069673482969185</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-3.440633977000178</v>
+        <v>-3.44303971640475</v>
       </c>
       <c r="E1914" t="n">
-        <v>1.704711631827466</v>
+        <v>1.703749336065637</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.03055270992869069</v>
+        <v>-0.02852673918817367</v>
       </c>
       <c r="G1914" t="n">
-        <v>3.06299002098407</v>
+        <v>3.06420560342838</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-3.254146284623172</v>
+        <v>-3.256552024027744</v>
       </c>
       <c r="E1915" t="n">
-        <v>1.776804802788845</v>
+        <v>1.775842507027016</v>
       </c>
       <c r="F1915" t="n">
-        <v>0.1559349824483156</v>
+        <v>0.1579609531888326</v>
       </c>
       <c r="G1915" t="n">
-        <v>3.17238073042085</v>
+        <v>3.173596312865161</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-3.232997085719728</v>
+        <v>-3.235402825124301</v>
       </c>
       <c r="E1916" t="n">
-        <v>1.792965460587548</v>
+        <v>1.792003164825719</v>
       </c>
       <c r="F1916" t="n">
-        <v>0.1770841813517589</v>
+        <v>0.1791101520922759</v>
       </c>
       <c r="G1916" t="n">
-        <v>3.192771228000242</v>
+        <v>3.193986810444553</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-2.989231643736284</v>
+        <v>-2.991637383140857</v>
       </c>
       <c r="E1917" t="n">
-        <v>1.886252345727977</v>
+        <v>1.885290049966147</v>
       </c>
       <c r="F1917" t="n">
-        <v>0.1770841813517589</v>
+        <v>0.1791101520922759</v>
       </c>
       <c r="G1917" t="n">
-        <v>3.188551936347293</v>
+        <v>3.189767518791603</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,45 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.627896148301777</v>
+        <v>3.824307657527528</v>
       </c>
       <c r="C1918" t="n">
         <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-2.725203576543024</v>
+        <v>-2.992916438292105</v>
       </c>
       <c r="E1918" t="n">
-        <v>1.993987886525296</v>
+        <v>1.886902741825664</v>
       </c>
       <c r="F1918" t="n">
-        <v>0.3789495801677125</v>
+        <v>0.1774619575003478</v>
       </c>
       <c r="G1918" t="n">
-        <v>3.311795489556881</v>
+        <v>3.190902915956462</v>
+      </c>
+    </row>
+    <row r="1919">
+      <c r="A1919" s="2" t="n">
+        <v>45381</v>
+      </c>
+      <c r="B1919" t="n">
+        <v>3.641766166427691</v>
+      </c>
+      <c r="C1919" t="n">
+        <v>2.97195201446704</v>
+      </c>
+      <c r="D1919" t="n">
+        <v>-2.992916438292105</v>
+      </c>
+      <c r="E1919" t="n">
+        <v>1.886902741825664</v>
+      </c>
+      <c r="F1919" t="n">
+        <v>0.1774619575003478</v>
+      </c>
+      <c r="G1919" t="n">
+        <v>2.965015811453408</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240330.xlsx
+++ b/tame_output/ON/bt/strategyON_20240330.xlsx
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-71.5%</t>
+          <t>-70.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.8%</t>
+          <t>109.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.0%</t>
+          <t>92.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-561.5%</t>
+          <t>-561.3%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.6%</t>
+          <t>25.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-66.9%</t>
+          <t>-65.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.4%</t>
+          <t>90.9%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>507.4%</t>
+          <t>508.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-460.9%</t>
+          <t>-434.1%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>24.2%</t>
+          <t>26.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-225.0%</t>
+          <t>-224.9%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1160,17 +1160,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>20.2%</t>
+          <t>22.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>43.7%</t>
+          <t>43.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-62.9%</t>
+          <t>-63.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-9.6%</t>
+          <t>-9.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-187.5%</t>
+          <t>-176.8%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-20.6%</t>
+          <t>-17.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>68.9%</t>
+          <t>70.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-287.1%</t>
+          <t>-287.3%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-13.9%</t>
+          <t>-11.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>56.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>112.5%</t>
+          <t>178.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-151.1%</t>
+          <t>-151.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-206.2%</t>
+          <t>-186.1%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>51.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>50.7%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>62.0%</t>
+          <t>64.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>41.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-172.7%</t>
+          <t>-172.8%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>42.2%</t>
+          <t>43.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -44049,22 +44049,22 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.27116857953743</v>
+        <v>3.271168579537429</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-0.6391093674693338</v>
+        <v>-0.6367036280647618</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.86094649524847</v>
+        <v>2.861908791010299</v>
       </c>
       <c r="F1848" t="n">
-        <v>1.35500359378675</v>
+        <v>1.352977623046232</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.929948822822001</v>
+        <v>3.92873324037769</v>
       </c>
     </row>
     <row r="1849">
@@ -44072,22 +44072,22 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382195</v>
+        <v>3.272760131382194</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-0.847113425822411</v>
+        <v>-0.844707686417839</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.782637016461165</v>
+        <v>2.783599312222993</v>
       </c>
       <c r="F1849" t="n">
-        <v>1.35500359378675</v>
+        <v>1.352977623046232</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.934840967375926</v>
+        <v>3.933625384931616</v>
       </c>
     </row>
     <row r="1850">
@@ -44095,22 +44095,22 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074626</v>
+        <v>3.251475576074625</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.117513388531296</v>
+        <v>-1.115107649126724</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.669558487715599</v>
+        <v>2.670520783477428</v>
       </c>
       <c r="F1850" t="n">
-        <v>1.084603631077864</v>
+        <v>1.082577660337347</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.767682446088583</v>
+        <v>3.766466863644273</v>
       </c>
     </row>
     <row r="1851">
@@ -44118,22 +44118,22 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911643</v>
+        <v>3.233800325911641</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.456671766119819</v>
+        <v>-1.454266026715246</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.526979435986639</v>
+        <v>2.527941731748468</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.7454452534893421</v>
+        <v>0.7434192827488249</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.557271718841919</v>
+        <v>3.556056136397609</v>
       </c>
     </row>
     <row r="1852">
@@ -44141,22 +44141,22 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.2235393782135</v>
+        <v>3.223539378213498</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-1.784688987847298</v>
+        <v>-1.782283248442725</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.416110837034416</v>
+        <v>2.417073132796244</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.4174280317618629</v>
+        <v>0.4154020610213457</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.3807996755442</v>
+        <v>3.379584093099889</v>
       </c>
     </row>
     <row r="1853">
@@ -44164,22 +44164,22 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.23116753741605</v>
+        <v>3.231167537416047</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-1.781352241338326</v>
+        <v>-1.778946501933754</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.425544286046573</v>
+        <v>2.426506581808402</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.4201200641808943</v>
+        <v>0.4180940934403771</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.390513645404187</v>
+        <v>3.389298062959877</v>
       </c>
     </row>
     <row r="1854">
@@ -44187,22 +44187,22 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382333</v>
+        <v>3.23598197738233</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-2.148063293004872</v>
+        <v>-2.1456575536003</v>
       </c>
       <c r="E1854" t="n">
-        <v>2.279966257423687</v>
+        <v>2.280928553185515</v>
       </c>
       <c r="F1854" t="n">
-        <v>0.05340901251434871</v>
+        <v>0.05138304177383146</v>
       </c>
       <c r="G1854" t="n">
-        <v>3.171593406447992</v>
+        <v>3.170377824003682</v>
       </c>
     </row>
     <row r="1855">
@@ -44210,22 +44210,22 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495504</v>
+        <v>3.278199702495501</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-2.533243683934944</v>
+        <v>-2.530837944530372</v>
       </c>
       <c r="E1855" t="n">
-        <v>2.124436639864521</v>
+        <v>2.12539893562635</v>
       </c>
       <c r="F1855" t="n">
-        <v>0.05340901251434871</v>
+        <v>0.05138304177383146</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.170135945260856</v>
+        <v>3.168920362816545</v>
       </c>
     </row>
     <row r="1856">
@@ -44233,22 +44233,22 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347061</v>
+        <v>3.299136146347058</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-2.876926457161607</v>
+        <v>-2.874520717757035</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.988732654028472</v>
+        <v>1.989694949790301</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.05449703951286949</v>
+        <v>-0.05652301025338674</v>
       </c>
       <c r="G1856" t="n">
-        <v>3.107161437499141</v>
+        <v>3.10594585505483</v>
       </c>
     </row>
     <row r="1857">
@@ -44256,22 +44256,22 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130023</v>
+        <v>3.28737757613002</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.234576807399955</v>
+        <v>-3.232171067995383</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.84177857258939</v>
+        <v>1.842740868351219</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.4121473897512176</v>
+        <v>-0.4141733604917349</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.88867728601239</v>
+        <v>2.887461703568079</v>
       </c>
     </row>
     <row r="1858">
@@ -44279,22 +44279,22 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.31588437417825</v>
+        <v>3.315884374178246</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-3.241237747622103</v>
+        <v>-3.238832008217531</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.840887123200791</v>
+        <v>1.84184941896262</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.4121473897512176</v>
+        <v>-0.4141733604917349</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.890450212712649</v>
+        <v>2.889234630268339</v>
       </c>
     </row>
     <row r="1859">
@@ -44302,22 +44302,22 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207819</v>
+        <v>3.305316798207815</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-3.673043540771891</v>
+        <v>-3.670637801367318</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.65449769340828</v>
+        <v>1.655459989170109</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.5485648861924846</v>
+        <v>-0.5505908569330018</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.794932602315293</v>
+        <v>2.793717019870983</v>
       </c>
     </row>
     <row r="1860">
@@ -44325,22 +44325,22 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310988</v>
+        <v>3.284619513310984</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-3.999476069639634</v>
+        <v>-3.997070330235062</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.512209456863273</v>
+        <v>1.513171752625103</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.6310331366996327</v>
+        <v>-0.6330591074401499</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.733736427013095</v>
+        <v>2.732520844568785</v>
       </c>
     </row>
     <row r="1861">
@@ -44348,22 +44348,22 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.30584953900654</v>
+        <v>3.305849539006536</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-4.001040220749937</v>
+        <v>-3.998634481345365</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.510164388075117</v>
+        <v>1.511126683836946</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.6310331366996327</v>
+        <v>-0.6330591074401499</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.73231701866906</v>
+        <v>2.73110143622475</v>
       </c>
     </row>
     <row r="1862">
@@ -44371,22 +44371,22 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.31108639130943</v>
+        <v>3.311086391309426</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-4.364666465650251</v>
+        <v>-4.362260726245678</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.371201450349234</v>
+        <v>1.372163746111063</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.7292547735667585</v>
+        <v>-0.7312807443072757</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.679871596783026</v>
+        <v>2.678656014338716</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970911</v>
+        <v>3.304715716970907</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-4.362239401121532</v>
+        <v>-4.35983366171696</v>
       </c>
       <c r="E1863" t="n">
-        <v>1.371426791166553</v>
+        <v>1.372389086928381</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.7295875553739102</v>
+        <v>-0.7316135261144274</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.678926442704567</v>
+        <v>2.677710860260257</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330528</v>
+        <v>3.300815818330525</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-4.77082817830221</v>
+        <v>-4.768422438897638</v>
       </c>
       <c r="E1864" t="n">
-        <v>1.20675282430904</v>
+        <v>1.207715120070869</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.138176332554589</v>
+        <v>-1.140202303295106</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.432534720410919</v>
+        <v>2.431319137966609</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191743</v>
+        <v>3.30261819419174</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-5.183810662443304</v>
+        <v>-5.181404923038731</v>
       </c>
       <c r="E1865" t="n">
-        <v>1.036745263124063</v>
+        <v>1.037707558885892</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.138176332554589</v>
+        <v>-1.140202303295106</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.42772015288238</v>
+        <v>2.426504570438069</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108645</v>
+        <v>3.305023265108642</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-5.600202536730301</v>
+        <v>-5.597796797325729</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.868182564018142</v>
+        <v>0.8691448597799707</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.138176332554589</v>
+        <v>-1.140202303295106</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.425714203491257</v>
+        <v>2.424498621046947</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097826</v>
+        <v>3.341378723097824</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-5.976879547260146</v>
+        <v>-5.974473807855573</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.7277704504748832</v>
+        <v>0.7287327462367119</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.138176332554589</v>
+        <v>-1.140202303295106</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.435972894159936</v>
+        <v>2.434757311715626</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094122</v>
+        <v>3.37443904309412</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-5.990594411585257</v>
+        <v>-5.988188672180685</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.7183840698905337</v>
+        <v>0.7193463656523629</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.138176332554589</v>
+        <v>-1.140202303295106</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.432072459305631</v>
+        <v>2.430856876861321</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199291</v>
+        <v>3.405960511199289</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-6.303419210830237</v>
+        <v>-6.301013471425664</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.5916590702475428</v>
+        <v>0.592621366009372</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.138176332554589</v>
+        <v>-1.140202303295106</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.430477379360632</v>
+        <v>2.429261796916322</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.4246333549696</v>
+        <v>3.424633354969598</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-6.308232249295574</v>
+        <v>-6.305826509891001</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.5935128307906159</v>
+        <v>0.5944751265524451</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.139722967257375</v>
+        <v>-1.141748937997892</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.433328374468168</v>
+        <v>2.432112792023858</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923093</v>
+        <v>3.419979433923091</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-6.74158135740581</v>
+        <v>-6.739175618001237</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.4161468830121184</v>
+        <v>0.4171091787739476</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.139722967257375</v>
+        <v>-1.141748937997892</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.429302069933765</v>
+        <v>2.428086487489455</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297755</v>
+        <v>3.458100091297753</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.124582746148441</v>
+        <v>-7.122177006743868</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.262844226193482</v>
+        <v>0.2638065219553112</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.139722967257375</v>
+        <v>-1.141748937997892</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.429199968612181</v>
+        <v>2.427984386167871</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317621</v>
+        <v>3.44775050131762</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.499568072319718</v>
+        <v>-7.497162332915146</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.1154216116964011</v>
+        <v>0.1163839074582302</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.514708293428652</v>
+        <v>-1.516734264169169</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.206780288880845</v>
+        <v>2.205564706436535</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737175</v>
+        <v>3.503515506737174</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-7.85909839482372</v>
+        <v>-7.856692655419147</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.02304021400714928</v>
+        <v>-0.02207791824532013</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.514708293428652</v>
+        <v>-1.516734264169169</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.212130592178895</v>
+        <v>2.210915009734585</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341318</v>
+        <v>3.503170282341317</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.185498423488733</v>
+        <v>-8.18309268408416</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.1456842055159768</v>
+        <v>-0.1447219097541477</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.841108322093665</v>
+        <v>-1.843134292834182</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.024206594937065</v>
+        <v>2.022991012492755</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776682</v>
+        <v>3.50044609677668</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.179022276695173</v>
+        <v>-8.176616537290601</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.1400519961767843</v>
+        <v>-0.1390897004149552</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.834632175300105</v>
+        <v>-1.836658146040622</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.03113403363497</v>
+        <v>2.029918451190659</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407494</v>
+        <v>3.492445136407495</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.175331351738762</v>
+        <v>-8.17292561233419</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.1385756261942199</v>
+        <v>-0.1376133304323908</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.834632175300105</v>
+        <v>-1.836658146040622</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.03113403363497</v>
+        <v>2.029918451190659</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.379589527068626</v>
+        <v>-8.377183787664054</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.2147656992075229</v>
+        <v>-0.2138034034456942</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.962271119914094</v>
+        <v>-1.964297090654611</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.960063863985218</v>
+        <v>1.958848281540909</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199886</v>
+        <v>3.496848329199887</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.540228553556991</v>
+        <v>-8.537822814152419</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.2745387553184329</v>
+        <v>-0.2735764595566041</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.07700459291649</v>
+        <v>-2.079030563657007</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.895706334668217</v>
+        <v>1.894490752223907</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910629</v>
+        <v>3.49996816391063</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.466758721889542</v>
+        <v>-8.46435298248497</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.2297791211580322</v>
+        <v>-0.2288168253962031</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.003534761249041</v>
+        <v>-2.005560731989558</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.955159935162108</v>
+        <v>1.953944352717797</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078597</v>
+        <v>3.490055666078598</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.641883139276086</v>
+        <v>-8.639477399871513</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.285273667365133</v>
+        <v>-0.2843113716033039</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.178659178635585</v>
+        <v>-2.180685149376102</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.864640505477698</v>
+        <v>1.863424923033388</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.48587501888027</v>
+        <v>3.485875018880271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-8.876335233290575</v>
+        <v>-8.873929493886003</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.3862736698725246</v>
+        <v>-0.3853113741106955</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.178659178635585</v>
+        <v>-2.180685149376102</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.857421340576102</v>
+        <v>1.856205758131792</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234395</v>
+        <v>3.480688917234396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.164139077827814</v>
+        <v>-9.161733338423241</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.5080673984613964</v>
+        <v>-0.5071051026995672</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.466463023172823</v>
+        <v>-2.46848899391334</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.678066843079783</v>
+        <v>1.676851260635473</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860585</v>
+        <v>3.493712438860586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.393963524991639</v>
+        <v>-9.391557785587066</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.5988813874883698</v>
+        <v>-0.5979190917265411</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.629110560242984</v>
+        <v>-2.631136530983501</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.581594110676243</v>
+        <v>1.580378528231933</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767398</v>
+        <v>3.492098065767399</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.625992444727901</v>
+        <v>-9.623586705323328</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.6889992267537601</v>
+        <v>-0.688036930991931</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.691123257431407</v>
+        <v>-2.693149228171924</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.547080220992304</v>
+        <v>1.545864638547993</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792543</v>
+        <v>3.573670449792544</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.573976930759088</v>
+        <v>-9.571571191354515</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.6642026854798342</v>
+        <v>-0.663240389718005</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.691123257431407</v>
+        <v>-2.693149228171924</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.551070556678704</v>
+        <v>1.549854974234394</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628921</v>
+        <v>3.600034689628922</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.715648772483208</v>
+        <v>-9.713243033078635</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.722346649068224</v>
+        <v>-0.7213843533063948</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.691123257431407</v>
+        <v>-2.693149228171924</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.549595329779963</v>
+        <v>1.548379747335653</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.518379366755211</v>
+        <v>-9.515973627350638</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.6283854766121526</v>
+        <v>-0.6274231808503234</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.493853851703409</v>
+        <v>-2.495879822443926</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.683010383381634</v>
+        <v>1.681794800937324</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.319227259518112</v>
+        <v>-9.316821520113539</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.5617757673639958</v>
+        <v>-0.5608134716021671</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.328531325753596</v>
+        <v>-2.330557296494113</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.769152765304839</v>
+        <v>1.767937182860529</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-9.0933821067987</v>
+        <v>-9.090976367394127</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.4618586332400225</v>
+        <v>-0.4608963374781934</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.286604650166432</v>
+        <v>-2.288630620906949</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.803887843693346</v>
+        <v>1.802672261249036</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.807107294476005</v>
+        <v>-8.804701555071432</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.3462095637548859</v>
+        <v>-0.3452472679930567</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.286604650166432</v>
+        <v>-2.288630620906949</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.805026988249405</v>
+        <v>1.803811405805094</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116217</v>
+        <v>3.710931958116218</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.580311467402671</v>
+        <v>-8.577905727998099</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.2528574587634447</v>
+        <v>-0.2518951630016155</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.218490705544887</v>
+        <v>-2.220516676285405</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.848529129184439</v>
+        <v>1.847313546740129</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.296402736473922</v>
+        <v>-8.29399699706935</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.1335602621533085</v>
+        <v>-0.1325979663914794</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.218490705544887</v>
+        <v>-2.220516676285405</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.854262833423076</v>
+        <v>1.853047250978765</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.049415486280971</v>
+        <v>-8.047009746876398</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.04450262446999309</v>
+        <v>-0.04354032870816393</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.971503455351935</v>
+        <v>-1.973529426092453</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.992717921144981</v>
+        <v>1.991502338700672</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-7.785578619076902</v>
+        <v>-7.783172879672329</v>
       </c>
       <c r="E1895" t="n">
-        <v>0.05114864109872697</v>
+        <v>0.05211093686055568</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.971503455351935</v>
+        <v>-1.973529426092453</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.982834439832074</v>
+        <v>1.981618857387764</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-7.518336818208505</v>
+        <v>-7.515931078803932</v>
       </c>
       <c r="E1896" t="n">
-        <v>0.1562108009467118</v>
+        <v>0.157173096708541</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.971503455351935</v>
+        <v>-1.973529426092453</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.9809998793327</v>
+        <v>1.97978429688839</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-7.242527654808021</v>
+        <v>-7.240121915403448</v>
       </c>
       <c r="E1897" t="n">
-        <v>0.2662341513334447</v>
+        <v>0.2671964470952735</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.882484147073202</v>
+        <v>-1.884510117813719</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.034111149326479</v>
+        <v>2.03289556688217</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-6.973460067041041</v>
+        <v>-6.971054327636469</v>
       </c>
       <c r="E1898" t="n">
-        <v>0.37452969258573</v>
+        <v>0.3754919883475591</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.613416559306223</v>
+        <v>-1.61544253004674</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.196220208132161</v>
+        <v>2.19500462568785</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-6.709400128718245</v>
+        <v>-6.706994389313673</v>
       </c>
       <c r="E1899" t="n">
-        <v>0.4668933517530962</v>
+        <v>0.4678556475149254</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.349356620983426</v>
+        <v>-1.351382591723943</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.341395854964086</v>
+        <v>2.340180272519776</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309729</v>
+        <v>3.83324917230973</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-6.002320505213407</v>
+        <v>-5.999914765808835</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.7469381674947306</v>
+        <v>0.7479004632565598</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.349356620983426</v>
+        <v>-1.351382591723943</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.338608821303785</v>
+        <v>2.337393238859475</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858731</v>
+        <v>3.839370871858732</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-5.752679475227455</v>
+        <v>-5.750273735822883</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.8471382033769528</v>
+        <v>0.8481004991387819</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.099715590997475</v>
+        <v>-1.101741561737992</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.488737063183198</v>
+        <v>2.487521480738887</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-5.49813757588638</v>
+        <v>-5.495731836481808</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.9483217843341398</v>
+        <v>0.949284080095969</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.8451736916563992</v>
+        <v>-0.8471996623969162</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.6408290240086</v>
+        <v>2.63961344156429</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761808</v>
+        <v>3.787326853761809</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-5.264656353656782</v>
+        <v>-5.262250614252209</v>
       </c>
       <c r="E1903" t="n">
-        <v>1.049638702063832</v>
+        <v>1.050600997825661</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.6116924694268007</v>
+        <v>-0.6137184401673177</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.788842186184211</v>
+        <v>2.787626603739901</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-5.084947823512909</v>
+        <v>-5.082542084108336</v>
       </c>
       <c r="E1904" t="n">
-        <v>1.118629903808422</v>
+        <v>1.11959219957025</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.5545209652641045</v>
+        <v>-0.5565469360046216</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.82025287836887</v>
+        <v>2.81903729592456</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-4.952672349882023</v>
+        <v>-4.95026661047745</v>
       </c>
       <c r="E1905" t="n">
-        <v>1.166907580007803</v>
+        <v>1.167869875769632</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.4222454916332179</v>
+        <v>-0.4242714623737349</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.894985649294429</v>
+        <v>2.893770066850119</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-4.76207267520887</v>
+        <v>-4.759666935804297</v>
       </c>
       <c r="E1906" t="n">
-        <v>1.245962510564701</v>
+        <v>1.24692480632653</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.231645816960065</v>
+        <v>-0.2336717877005821</v>
       </c>
       <c r="G1906" t="n">
-        <v>3.012160514785958</v>
+        <v>3.010944932341647</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-4.513072876525289</v>
+        <v>-4.510667137120716</v>
       </c>
       <c r="E1907" t="n">
-        <v>1.358468771261792</v>
+        <v>1.359431067023621</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.231645816960065</v>
+        <v>-0.2336717877005821</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.025066856009616</v>
+        <v>3.023851273565306</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077646</v>
+        <v>3.692928280077645</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-4.618662866298394</v>
+        <v>-4.616257126893821</v>
       </c>
       <c r="E1908" t="n">
-        <v>1.188256845753332</v>
+        <v>1.189219141515161</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.3372358067331694</v>
+        <v>-0.3392617774736864</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.833736932546535</v>
+        <v>2.832521350102225</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457904</v>
+        <v>3.770419008457902</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-4.339635570642766</v>
+        <v>-4.337229831238194</v>
       </c>
       <c r="E1909" t="n">
-        <v>1.348412105892669</v>
+        <v>1.349374401654498</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.3372358067331694</v>
+        <v>-0.3392617774736864</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.882281274423621</v>
+        <v>2.881065691979311</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-4.062897395971953</v>
+        <v>-4.060491656567381</v>
       </c>
       <c r="E1910" t="n">
-        <v>1.462486387746989</v>
+        <v>1.463448683508818</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.1554191456232436</v>
+        <v>-0.1574451163637606</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.994750283075571</v>
+        <v>2.993534700631261</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-3.936004989536884</v>
+        <v>-3.933599250132311</v>
       </c>
       <c r="E1911" t="n">
-        <v>1.504529364067538</v>
+        <v>1.505491659829368</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.02852673918817367</v>
+        <v>-0.03055270992869069</v>
       </c>
       <c r="G1911" t="n">
-        <v>3.062171740683135</v>
+        <v>3.060956158238825</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-3.748417481626957</v>
+        <v>-3.746011742222384</v>
       </c>
       <c r="E1912" t="n">
-        <v>1.572603755136416</v>
+        <v>1.573566050898245</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.02852673918817367</v>
+        <v>-0.03055270992869069</v>
       </c>
       <c r="G1912" t="n">
-        <v>3.055211128588042</v>
+        <v>3.053995546143732</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-3.506269088173099</v>
+        <v>-3.503863348768526</v>
       </c>
       <c r="E1913" t="n">
-        <v>1.683925466899102</v>
+        <v>1.684887762660931</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.02852673918817367</v>
+        <v>-0.03055270992869069</v>
       </c>
       <c r="G1913" t="n">
-        <v>3.069673482969185</v>
+        <v>3.068457900524875</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-3.44303971640475</v>
+        <v>-3.440633977000178</v>
       </c>
       <c r="E1914" t="n">
-        <v>1.703749336065637</v>
+        <v>1.704711631827466</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.02852673918817367</v>
+        <v>-0.03055270992869069</v>
       </c>
       <c r="G1914" t="n">
-        <v>3.06420560342838</v>
+        <v>3.06299002098407</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-3.256552024027744</v>
+        <v>-3.254146284623172</v>
       </c>
       <c r="E1915" t="n">
-        <v>1.775842507027016</v>
+        <v>1.776804802788845</v>
       </c>
       <c r="F1915" t="n">
-        <v>0.1579609531888326</v>
+        <v>0.1559349824483156</v>
       </c>
       <c r="G1915" t="n">
-        <v>3.173596312865161</v>
+        <v>3.17238073042085</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-3.235402825124301</v>
+        <v>-3.232997085719728</v>
       </c>
       <c r="E1916" t="n">
-        <v>1.792003164825719</v>
+        <v>1.792965460587548</v>
       </c>
       <c r="F1916" t="n">
-        <v>0.1791101520922759</v>
+        <v>0.1770841813517589</v>
       </c>
       <c r="G1916" t="n">
-        <v>3.193986810444553</v>
+        <v>3.192771228000242</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-2.991637383140857</v>
+        <v>-2.989231643736284</v>
       </c>
       <c r="E1917" t="n">
-        <v>1.885290049966147</v>
+        <v>1.886252345727977</v>
       </c>
       <c r="F1917" t="n">
-        <v>0.1791101520922759</v>
+        <v>0.1770841813517589</v>
       </c>
       <c r="G1917" t="n">
-        <v>3.189767518791603</v>
+        <v>3.188551936347293</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527528</v>
+        <v>3.824307657527527</v>
       </c>
       <c r="C1918" t="n">
         <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-2.992916438292105</v>
+        <v>-2.725203576543024</v>
       </c>
       <c r="E1918" t="n">
-        <v>1.886902741825664</v>
+        <v>1.993987886525296</v>
       </c>
       <c r="F1918" t="n">
-        <v>0.1774619575003478</v>
+        <v>0.3789495801677125</v>
       </c>
       <c r="G1918" t="n">
-        <v>3.190902915956462</v>
+        <v>3.311795489556881</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,19 +45682,19 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.641766166427691</v>
+        <v>3.64176616642769</v>
       </c>
       <c r="C1919" t="n">
         <v>2.97195201446704</v>
       </c>
       <c r="D1919" t="n">
-        <v>-2.992916438292105</v>
+        <v>-2.725203576543024</v>
       </c>
       <c r="E1919" t="n">
-        <v>1.886902741825664</v>
+        <v>1.993987886525296</v>
       </c>
       <c r="F1919" t="n">
-        <v>0.1774619575003478</v>
+        <v>0.3789495801677125</v>
       </c>
       <c r="G1919" t="n">
         <v>2.965015811453408</v>

--- a/tame_output/ON/bt/strategyON_20240330.xlsx
+++ b/tame_output/ON/bt/strategyON_20240330.xlsx
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537429</v>
+        <v>3.27116857953743</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911641</v>
+        <v>3.233800325911642</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416047</v>
+        <v>3.231167537416048</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.23598197738233</v>
+        <v>3.235981977382331</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495501</v>
+        <v>3.278199702495502</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.28737757613002</v>
+        <v>3.287377576130021</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178246</v>
+        <v>3.315884374178247</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207815</v>
+        <v>3.305316798207816</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310984</v>
+        <v>3.284619513310985</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309426</v>
+        <v>3.311086391309427</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970907</v>
+        <v>3.304715716970908</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330525</v>
+        <v>3.300815818330526</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.30261819419174</v>
+        <v>3.302618194191741</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108642</v>
+        <v>3.305023265108643</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097824</v>
+        <v>3.341378723097825</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.37443904309412</v>
+        <v>3.374439043094121</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199289</v>
+        <v>3.40596051119929</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969598</v>
+        <v>3.424633354969599</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923091</v>
+        <v>3.419979433923092</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297753</v>
+        <v>3.458100091297754</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.44775050131762</v>
+        <v>3.447750501317621</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737174</v>
+        <v>3.503515506737175</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341317</v>
+        <v>3.503170282341318</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50044609677668</v>
+        <v>3.500446096776681</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407495</v>
+        <v>3.492445136407496</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611697</v>
+        <v>3.502786823611698</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199887</v>
+        <v>3.496848329199888</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.49996816391063</v>
+        <v>3.499968163910631</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880271</v>
+        <v>3.485875018880272</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234396</v>
+        <v>3.480688917234397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767399</v>
+        <v>3.4920980657674</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628922</v>
+        <v>3.600034689628923</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410719</v>
+        <v>3.69156815841072</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240578</v>
+        <v>3.676837974240579</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282102</v>
+        <v>3.684840248282103</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457902</v>
+        <v>3.770419008457901</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.76033011118081</v>
+        <v>3.760330111180809</v>
       </c>
       <c r="C1910" t="n">
         <v>3.088001770449517</v>

--- a/tame_output/ON/bt/strategyON_20240330.xlsx
+++ b/tame_output/ON/bt/strategyON_20240330.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.5%</t>
+          <t>50.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>68.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>69.8%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.5%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.5%</t>
+          <t>-17.8%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-12.4%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>14.1%</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>54.0%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.6%</t>
+          <t>-4.5%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-70.2%</t>
+          <t>-70.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.4%</t>
+          <t>109.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>125.6%</t>
+          <t>125.7%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>92.4%</t>
+          <t>92.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -969,11 +969,11 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2024-02-27</t>
+          <t>2024-02-28</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>25.3%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-46.5%</t>
+          <t>-47.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-65.6%</t>
+          <t>-65.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>90.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>508.1%</t>
+          <t>505.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-434.1%</t>
+          <t>-437.3%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>26.6%</t>
+          <t>23.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>61.4%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1127,11 +1127,11 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2024-02-27</t>
+          <t>2024-02-28</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1155,22 +1155,22 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-36.2%</t>
+          <t>-37.1%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>22.3%</t>
+          <t>20.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>43.9%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-63.6%</t>
+          <t>-69.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-9.7%</t>
+          <t>-1.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-176.8%</t>
+          <t>-189.4%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-17.8%</t>
+          <t>-22.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>70.5%</t>
+          <t>69.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.7%</t>
+          <t>99.8%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1285,11 +1285,11 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-02-28</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-30.7%</t>
+          <t>-32.5%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-11.3%</t>
+          <t>-15.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.6%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>178.8%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-151.2%</t>
+          <t>-150.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-186.1%</t>
+          <t>-215.0%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>49.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>60.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.8%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.1%</t>
+          <t>96.2%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1443,11 +1443,11 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-02-28</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-26.4%</t>
+          <t>-28.0%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>48.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>41.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-14.0%</t>
+          <t>-15.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-149.5%</t>
+          <t>-143.4%</t>
         </is>
       </c>
     </row>
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.515973627350638</v>
+        <v>-9.804671114179751</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.6274231808503234</v>
+        <v>-0.7429021755819689</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.495879822443926</v>
+        <v>-2.784577309273039</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.681794800937324</v>
+        <v>1.508576308839856</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.316821520113539</v>
+        <v>-9.605519006942652</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.5608134716021671</v>
+        <v>-0.6762924663338121</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.330557296494113</v>
+        <v>-2.619254783323226</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.767937182860529</v>
+        <v>1.594718690763061</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-9.090976367394127</v>
+        <v>-9.379673854223242</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.4608963374781934</v>
+        <v>-0.5763753322098393</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.288630620906949</v>
+        <v>-2.577328107736062</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.802672261249036</v>
+        <v>1.629453769151568</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.804701555071432</v>
+        <v>-9.093399041900547</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.3452472679930567</v>
+        <v>-0.4607262627247026</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.288630620906949</v>
+        <v>-2.577328107736062</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.803811405805094</v>
+        <v>1.630592913707626</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.577905727998099</v>
+        <v>-8.866603214827213</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.2518951630016155</v>
+        <v>-0.3673741577332614</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.220516676285405</v>
+        <v>-2.509214163114518</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.847313546740129</v>
+        <v>1.674095054642661</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.29399699706935</v>
+        <v>-8.582694483898464</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.1325979663914794</v>
+        <v>-0.2480769611231253</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.220516676285405</v>
+        <v>-2.509214163114518</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.853047250978765</v>
+        <v>1.679828758881297</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.047009746876398</v>
+        <v>-8.335707233705513</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.04354032870816393</v>
+        <v>-0.1590193234398098</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.973529426092453</v>
+        <v>-2.262226912921566</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.991502338700672</v>
+        <v>1.818283846603203</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-7.783172879672329</v>
+        <v>-8.071870366501443</v>
       </c>
       <c r="E1895" t="n">
-        <v>0.05211093686055568</v>
+        <v>-0.06336805787108979</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.973529426092453</v>
+        <v>-2.262226912921566</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.981618857387764</v>
+        <v>1.808400365290296</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-7.515931078803932</v>
+        <v>-7.804628565633046</v>
       </c>
       <c r="E1896" t="n">
-        <v>0.157173096708541</v>
+        <v>0.04169410197689549</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.973529426092453</v>
+        <v>-2.262226912921566</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.97978429688839</v>
+        <v>1.806565804790922</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-7.240121915403448</v>
+        <v>-7.528819402232562</v>
       </c>
       <c r="E1897" t="n">
-        <v>0.2671964470952735</v>
+        <v>0.151717452363628</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.884510117813719</v>
+        <v>-2.173207604642832</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.03289556688217</v>
+        <v>1.859677074784701</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-6.971054327636469</v>
+        <v>-7.259751814465583</v>
       </c>
       <c r="E1898" t="n">
-        <v>0.3754919883475591</v>
+        <v>0.2600129936159137</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.61544253004674</v>
+        <v>-1.904140016875853</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.19500462568785</v>
+        <v>2.021786133590382</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-6.706994389313673</v>
+        <v>-6.995691876142787</v>
       </c>
       <c r="E1899" t="n">
-        <v>0.4678556475149254</v>
+        <v>0.3523766527832799</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.351382591723943</v>
+        <v>-1.640080078553057</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.340180272519776</v>
+        <v>2.166961780422308</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-5.999914765808835</v>
+        <v>-6.288612252637948</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.7479004632565598</v>
+        <v>0.6324214685249143</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.351382591723943</v>
+        <v>-1.640080078553057</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.337393238859475</v>
+        <v>2.164174746762007</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-5.750273735822883</v>
+        <v>-6.038971222651996</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.8481004991387819</v>
+        <v>0.7326215044071365</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.101741561737992</v>
+        <v>-1.390439048567105</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.487521480738887</v>
+        <v>2.314302988641419</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-5.495731836481808</v>
+        <v>-5.784429323310921</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.949284080095969</v>
+        <v>0.833805085364324</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.8471996623969162</v>
+        <v>-1.13589714922603</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.63961344156429</v>
+        <v>2.466394949466822</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-5.262250614252209</v>
+        <v>-5.550948101081322</v>
       </c>
       <c r="E1903" t="n">
-        <v>1.050600997825661</v>
+        <v>0.9351220030940155</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.6137184401673177</v>
+        <v>-0.9024159269964311</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.787626603739901</v>
+        <v>2.614408111642433</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-5.082542084108336</v>
+        <v>-5.371239570937449</v>
       </c>
       <c r="E1904" t="n">
-        <v>1.11959219957025</v>
+        <v>1.004113204838605</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.5565469360046216</v>
+        <v>-0.845244422833735</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.81903729592456</v>
+        <v>2.645818803827092</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-4.95026661047745</v>
+        <v>-5.238964097306563</v>
       </c>
       <c r="E1905" t="n">
-        <v>1.167869875769632</v>
+        <v>1.052390881037987</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.4242714623737349</v>
+        <v>-0.7129689492028484</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.893770066850119</v>
+        <v>2.720551574752651</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-4.759666935804297</v>
+        <v>-5.04836442263341</v>
       </c>
       <c r="E1906" t="n">
-        <v>1.24692480632653</v>
+        <v>1.131445811594885</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.2336717877005821</v>
+        <v>-0.5223692745296955</v>
       </c>
       <c r="G1906" t="n">
-        <v>3.010944932341647</v>
+        <v>2.837726440244179</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-4.510667137120716</v>
+        <v>-4.799364623949829</v>
       </c>
       <c r="E1907" t="n">
-        <v>1.359431067023621</v>
+        <v>1.243952072291976</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.2336717877005821</v>
+        <v>-0.5223692745296955</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.023851273565306</v>
+        <v>2.850632781467838</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-4.616257126893821</v>
+        <v>-4.904954613722934</v>
       </c>
       <c r="E1908" t="n">
-        <v>1.189219141515161</v>
+        <v>1.073740146783515</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.3392617774736864</v>
+        <v>-0.6279592643027998</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.832521350102225</v>
+        <v>2.659302858004757</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-4.337229831238194</v>
+        <v>-4.625927318067307</v>
       </c>
       <c r="E1909" t="n">
-        <v>1.349374401654498</v>
+        <v>1.233895406922853</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.3392617774736864</v>
+        <v>-0.6279592643027998</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.881065691979311</v>
+        <v>2.707847199881843</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-4.060491656567381</v>
+        <v>-4.349189143396494</v>
       </c>
       <c r="E1910" t="n">
-        <v>1.463448683508818</v>
+        <v>1.347969688777173</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.1574451163637606</v>
+        <v>-0.446142603192874</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.993534700631261</v>
+        <v>2.820316208533793</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-3.933599250132311</v>
+        <v>-4.222296736961423</v>
       </c>
       <c r="E1911" t="n">
-        <v>1.505491659829368</v>
+        <v>1.390012665097722</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.03055270992869069</v>
+        <v>-0.3192501967578041</v>
       </c>
       <c r="G1911" t="n">
-        <v>3.060956158238825</v>
+        <v>2.887737666141357</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-3.746011742222384</v>
+        <v>-4.034709229051497</v>
       </c>
       <c r="E1912" t="n">
-        <v>1.573566050898245</v>
+        <v>1.4580870561666</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.03055270992869069</v>
+        <v>-0.3192501967578041</v>
       </c>
       <c r="G1912" t="n">
-        <v>3.053995546143732</v>
+        <v>2.880777054046264</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-3.503863348768526</v>
+        <v>-3.792560835597639</v>
       </c>
       <c r="E1913" t="n">
-        <v>1.684887762660931</v>
+        <v>1.569408767929286</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.03055270992869069</v>
+        <v>-0.3192501967578041</v>
       </c>
       <c r="G1913" t="n">
-        <v>3.068457900524875</v>
+        <v>2.895239408427407</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-3.440633977000178</v>
+        <v>-3.729331463829291</v>
       </c>
       <c r="E1914" t="n">
-        <v>1.704711631827466</v>
+        <v>1.589232637095821</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.03055270992869069</v>
+        <v>-0.3192501967578041</v>
       </c>
       <c r="G1914" t="n">
-        <v>3.06299002098407</v>
+        <v>2.889771528886602</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-3.254146284623172</v>
+        <v>-3.542843771452285</v>
       </c>
       <c r="E1915" t="n">
-        <v>1.776804802788845</v>
+        <v>1.6613258080572</v>
       </c>
       <c r="F1915" t="n">
-        <v>0.1559349824483156</v>
+        <v>-0.1327625043807978</v>
       </c>
       <c r="G1915" t="n">
-        <v>3.17238073042085</v>
+        <v>2.999162238323382</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-3.232997085719728</v>
+        <v>-3.521694572548841</v>
       </c>
       <c r="E1916" t="n">
-        <v>1.792965460587548</v>
+        <v>1.677486465855903</v>
       </c>
       <c r="F1916" t="n">
-        <v>0.1770841813517589</v>
+        <v>-0.1116133054773545</v>
       </c>
       <c r="G1916" t="n">
-        <v>3.192771228000242</v>
+        <v>3.019552735902774</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-2.989231643736284</v>
+        <v>-3.277929130565397</v>
       </c>
       <c r="E1917" t="n">
-        <v>1.886252345727977</v>
+        <v>1.770773350996331</v>
       </c>
       <c r="F1917" t="n">
-        <v>0.1770841813517589</v>
+        <v>-0.1116133054773545</v>
       </c>
       <c r="G1917" t="n">
-        <v>3.188551936347293</v>
+        <v>3.015333444249825</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-2.725203576543024</v>
+        <v>-3.013901063372137</v>
       </c>
       <c r="E1918" t="n">
-        <v>1.993987886525296</v>
+        <v>1.878508891793651</v>
       </c>
       <c r="F1918" t="n">
-        <v>0.3789495801677125</v>
+        <v>0.09025209333859907</v>
       </c>
       <c r="G1918" t="n">
-        <v>3.311795489556881</v>
+        <v>3.138576997459413</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.64176616642769</v>
+        <v>3.421894867663107</v>
       </c>
       <c r="C1919" t="n">
         <v>2.97195201446704</v>
       </c>
       <c r="D1919" t="n">
-        <v>-2.725203576543024</v>
+        <v>-2.757482876097249</v>
       </c>
       <c r="E1919" t="n">
-        <v>1.993987886525296</v>
+        <v>1.868602439714394</v>
       </c>
       <c r="F1919" t="n">
-        <v>0.3789495801677125</v>
+        <v>0.09025209333859907</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.965015811453408</v>
+        <v>3.0261032704702</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240330.xlsx
+++ b/tame_output/ON/bt/strategyON_20240330.xlsx
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>68.6%</t>
+          <t>72.2%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>29.3%</t>
+          <t>28.9%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>31.7%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,25 +801,25 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2024-03-04</t>
+          <t>2021-03-21</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2021-03-24</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-11.3%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>59.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.2%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.5%</t>
+          <t>-4.9%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-14.4%</t>
+          <t>-3.9%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-70.4%</t>
+          <t>-68.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.7%</t>
+          <t>108.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>125.7%</t>
+          <t>123.8%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-561.3%</t>
+          <t>-561.6%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.7%</t>
+          <t>-46.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-65.1%</t>
+          <t>-63.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.8%</t>
+          <t>89.9%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>505.2%</t>
+          <t>499.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-437.3%</t>
+          <t>-418.4%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>23.7%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>61.4%</t>
+          <t>60.8%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-224.9%</t>
+          <t>-219.2%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-37.1%</t>
+          <t>-36.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,32 +1165,32 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>20.1%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>43.7%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-69.5%</t>
+          <t>-79.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-1.4%</t>
+          <t>-3.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-189.4%</t>
+          <t>-171.3%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-22.0%</t>
+          <t>-21.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.8%</t>
+          <t>99.7%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-287.3%</t>
+          <t>-283.3%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-32.5%</t>
+          <t>-32.3%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-15.9%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>43.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-150.0%</t>
+          <t>-148.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-215.0%</t>
+          <t>-211.7%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>59.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>49.9%</t>
+          <t>49.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60.5%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-172.8%</t>
+          <t>-170.4%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-28.0%</t>
+          <t>-27.8%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>48.9%</t>
+          <t>54.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>41.6%</t>
+          <t>41.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.0%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-143.4%</t>
+          <t>-130.9%</t>
         </is>
       </c>
     </row>
@@ -44049,22 +44049,22 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.27116857953743</v>
+        <v>3.271168579537429</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-0.6367036280647618</v>
+        <v>-0.4422140330987777</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.861908791010299</v>
+        <v>2.939704628996693</v>
       </c>
       <c r="F1848" t="n">
-        <v>1.352977623046232</v>
+        <v>1.393312858698349</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.92873324037769</v>
+        <v>3.952934381768961</v>
       </c>
     </row>
     <row r="1849">
@@ -44072,22 +44072,22 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382195</v>
+        <v>3.272760131382194</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-0.844707686417839</v>
+        <v>-0.6502180914518549</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.783599312222993</v>
+        <v>2.861395150209387</v>
       </c>
       <c r="F1849" t="n">
-        <v>1.352977623046232</v>
+        <v>1.393312858698349</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.933625384931616</v>
+        <v>3.957826526322886</v>
       </c>
     </row>
     <row r="1850">
@@ -44095,22 +44095,22 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074626</v>
+        <v>3.251475576074625</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.115107649126724</v>
+        <v>-0.9206180541607403</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.670520783477428</v>
+        <v>2.748316621463821</v>
       </c>
       <c r="F1850" t="n">
-        <v>1.082577660337347</v>
+        <v>1.122912895989464</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.766466863644273</v>
+        <v>3.790668005035543</v>
       </c>
     </row>
     <row r="1851">
@@ -44118,22 +44118,22 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911643</v>
+        <v>3.233800325911642</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.454266026715246</v>
+        <v>-1.259776431749262</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.527941731748468</v>
+        <v>2.605737569734861</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.7434192827488249</v>
+        <v>0.783754518400942</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.556056136397609</v>
+        <v>3.580257277788879</v>
       </c>
     </row>
     <row r="1852">
@@ -44141,22 +44141,22 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.2235393782135</v>
+        <v>3.223539378213498</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-1.782283248442725</v>
+        <v>-1.587793653476741</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.417073132796244</v>
+        <v>2.494868970782638</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.4154020610213457</v>
+        <v>0.4557372966734629</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.379584093099889</v>
+        <v>3.40378523449116</v>
       </c>
     </row>
     <row r="1853">
@@ -44164,22 +44164,22 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.23116753741605</v>
+        <v>3.231167537416048</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-1.778946501933754</v>
+        <v>-1.58445690696777</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.426506581808402</v>
+        <v>2.504302419794795</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.4180940934403771</v>
+        <v>0.4584293290924942</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.389298062959877</v>
+        <v>3.413499204351147</v>
       </c>
     </row>
     <row r="1854">
@@ -44187,22 +44187,22 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382333</v>
+        <v>3.235981977382331</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-2.1456575536003</v>
+        <v>-1.951167958634316</v>
       </c>
       <c r="E1854" t="n">
-        <v>2.280928553185515</v>
+        <v>2.358724391171909</v>
       </c>
       <c r="F1854" t="n">
-        <v>0.05138304177383146</v>
+        <v>0.09171827742594862</v>
       </c>
       <c r="G1854" t="n">
-        <v>3.170377824003682</v>
+        <v>3.194578965394952</v>
       </c>
     </row>
     <row r="1855">
@@ -44210,22 +44210,22 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495504</v>
+        <v>3.278199702495502</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-2.530837944530372</v>
+        <v>-2.336348349564388</v>
       </c>
       <c r="E1855" t="n">
-        <v>2.12539893562635</v>
+        <v>2.203194773612744</v>
       </c>
       <c r="F1855" t="n">
-        <v>0.05138304177383146</v>
+        <v>0.09171827742594862</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.168920362816545</v>
+        <v>3.193121504207815</v>
       </c>
     </row>
     <row r="1856">
@@ -44233,22 +44233,22 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347061</v>
+        <v>3.299136146347059</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-2.874520717757035</v>
+        <v>-2.680031122791051</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.989694949790301</v>
+        <v>2.067490787776695</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.05652301025338674</v>
+        <v>-0.01618777460126958</v>
       </c>
       <c r="G1856" t="n">
-        <v>3.10594585505483</v>
+        <v>3.130146996446101</v>
       </c>
     </row>
     <row r="1857">
@@ -44256,22 +44256,22 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130023</v>
+        <v>3.287377576130022</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.232171067995383</v>
+        <v>-3.037681473029399</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.842740868351219</v>
+        <v>1.920536706337613</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.4141733604917349</v>
+        <v>-0.3738381248396177</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.887461703568079</v>
+        <v>2.911662844959349</v>
       </c>
     </row>
     <row r="1858">
@@ -44279,22 +44279,22 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.31588437417825</v>
+        <v>3.315884374178248</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-3.238832008217531</v>
+        <v>-3.044342413251547</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.84184941896262</v>
+        <v>1.919645256949013</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.4141733604917349</v>
+        <v>-0.3738381248396177</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.889234630268339</v>
+        <v>2.913435771659609</v>
       </c>
     </row>
     <row r="1859">
@@ -44302,22 +44302,22 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207819</v>
+        <v>3.305316798207818</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-3.670637801367318</v>
+        <v>-3.476148206401334</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.655459989170109</v>
+        <v>1.733255827156503</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.5505908569330018</v>
+        <v>-0.5102556212808846</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.793717019870983</v>
+        <v>2.817918161262253</v>
       </c>
     </row>
     <row r="1860">
@@ -44325,22 +44325,22 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310988</v>
+        <v>3.284619513310986</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-3.997070330235062</v>
+        <v>-3.802580735269078</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.513171752625103</v>
+        <v>1.590967590611496</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.6330591074401499</v>
+        <v>-0.5927238717880328</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.732520844568785</v>
+        <v>2.756721985960055</v>
       </c>
     </row>
     <row r="1861">
@@ -44348,22 +44348,22 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.30584953900654</v>
+        <v>3.305849539006538</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-3.998634481345365</v>
+        <v>-3.804144886379381</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.511126683836946</v>
+        <v>1.58892252182334</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.6330591074401499</v>
+        <v>-0.5927238717880328</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.73110143622475</v>
+        <v>2.75530257761602</v>
       </c>
     </row>
     <row r="1862">
@@ -44371,22 +44371,22 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.31108639130943</v>
+        <v>3.311086391309428</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-4.362260726245678</v>
+        <v>-4.167771131279694</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.372163746111063</v>
+        <v>1.449959584097456</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.7312807443072757</v>
+        <v>-0.6909455086551586</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.678656014338716</v>
+        <v>2.702857155729986</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970911</v>
+        <v>3.304715716970909</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-4.35983366171696</v>
+        <v>-4.165344066750976</v>
       </c>
       <c r="E1863" t="n">
-        <v>1.372389086928381</v>
+        <v>1.450184924914775</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.7316135261144274</v>
+        <v>-0.6912782904623102</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.677710860260257</v>
+        <v>2.701912001651527</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330528</v>
+        <v>3.300815818330526</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-4.768422438897638</v>
+        <v>-4.573932843931654</v>
       </c>
       <c r="E1864" t="n">
-        <v>1.207715120070869</v>
+        <v>1.285510958057263</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.140202303295106</v>
+        <v>-1.099867067642989</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.431319137966609</v>
+        <v>2.455520279357879</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191743</v>
+        <v>3.302618194191741</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-5.181404923038731</v>
+        <v>-4.986915328072748</v>
       </c>
       <c r="E1865" t="n">
-        <v>1.037707558885892</v>
+        <v>1.115503396872286</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.140202303295106</v>
+        <v>-1.099867067642989</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.426504570438069</v>
+        <v>2.45070571182934</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108645</v>
+        <v>3.305023265108643</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-5.597796797325729</v>
+        <v>-5.403307202359746</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.8691448597799707</v>
+        <v>0.9469406977663639</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.140202303295106</v>
+        <v>-1.099867067642989</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.424498621046947</v>
+        <v>2.448699762438217</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097826</v>
+        <v>3.341378723097824</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-5.974473807855573</v>
+        <v>-5.77998421288959</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.7287327462367119</v>
+        <v>0.8065285842231051</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.140202303295106</v>
+        <v>-1.099867067642989</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.434757311715626</v>
+        <v>2.458958453106896</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094122</v>
+        <v>3.37443904309412</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-5.988188672180685</v>
+        <v>-5.793699077214701</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.7193463656523629</v>
+        <v>0.7971422036387561</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.140202303295106</v>
+        <v>-1.099867067642989</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.430856876861321</v>
+        <v>2.455058018252591</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199291</v>
+        <v>3.405960511199289</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-6.301013471425664</v>
+        <v>-6.106523876459681</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.592621366009372</v>
+        <v>0.6704172039957652</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.140202303295106</v>
+        <v>-1.099867067642989</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.429261796916322</v>
+        <v>2.453462938307592</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.4246333549696</v>
+        <v>3.424633354969598</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-6.305826509891001</v>
+        <v>-6.111336914925018</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.5944751265524451</v>
+        <v>0.6722709645388383</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.141748937997892</v>
+        <v>-1.101413702345774</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.432112792023858</v>
+        <v>2.456313933415128</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923093</v>
+        <v>3.419979433923091</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-6.739175618001237</v>
+        <v>-6.544686023035254</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.4171091787739476</v>
+        <v>0.4949050167603408</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.141748937997892</v>
+        <v>-1.101413702345774</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.428086487489455</v>
+        <v>2.452287628880725</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297755</v>
+        <v>3.458100091297753</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.122177006743868</v>
+        <v>-6.927687411777885</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.2638065219553112</v>
+        <v>0.3416023599417044</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.141748937997892</v>
+        <v>-1.101413702345774</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.427984386167871</v>
+        <v>2.452185527559141</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317621</v>
+        <v>3.44775050131762</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.497162332915146</v>
+        <v>-7.302672737949162</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.1163839074582302</v>
+        <v>0.1941797454446235</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.516734264169169</v>
+        <v>-1.476399028517052</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.205564706436535</v>
+        <v>2.229765847827805</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737175</v>
+        <v>3.503515506737173</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-7.856692655419147</v>
+        <v>-7.662203060453164</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.02207791824532013</v>
+        <v>0.0557179197410731</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.516734264169169</v>
+        <v>-1.476399028517052</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.210915009734585</v>
+        <v>2.235116151125855</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341318</v>
+        <v>3.503170282341316</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.18309268408416</v>
+        <v>-7.988603089118177</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.1447219097541477</v>
+        <v>-0.06692607176775445</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.843134292834182</v>
+        <v>-1.802799057182065</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.022991012492755</v>
+        <v>2.047192153884025</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776682</v>
+        <v>3.50044609677668</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.176616537290601</v>
+        <v>-7.982126942324618</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.1390897004149552</v>
+        <v>-0.06129386242856194</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.836658146040622</v>
+        <v>-1.796322910388505</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.029918451190659</v>
+        <v>2.05411959258193</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407494</v>
+        <v>3.492445136407492</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.17292561233419</v>
+        <v>-7.978436017368206</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.1376133304323908</v>
+        <v>-0.0598174924459971</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.836658146040622</v>
+        <v>-1.796322910388505</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.029918451190659</v>
+        <v>2.05411959258193</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611697</v>
+        <v>3.502786823611695</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.377183787664054</v>
+        <v>-8.182694192698069</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.2138034034456942</v>
+        <v>-0.1360075654593</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.964297090654611</v>
+        <v>-1.923961855002494</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.958848281540909</v>
+        <v>1.983049422932178</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199886</v>
+        <v>3.496848329199885</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.537822814152419</v>
+        <v>-8.343333219186434</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.2735764595566041</v>
+        <v>-0.19578062157021</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.079030563657007</v>
+        <v>-2.03869532800489</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.894490752223907</v>
+        <v>1.918691893615177</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910629</v>
+        <v>3.499968163910627</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.46435298248497</v>
+        <v>-8.269863387518985</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.2288168253962031</v>
+        <v>-0.1510209874098094</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.005560731989558</v>
+        <v>-1.965225496337441</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.953944352717797</v>
+        <v>1.978145494109068</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078597</v>
+        <v>3.490055666078595</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.639477399871513</v>
+        <v>-8.444987804905528</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.2843113716033039</v>
+        <v>-0.2065155336169098</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.180685149376102</v>
+        <v>-2.140349913723985</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.863424923033388</v>
+        <v>1.887626064424658</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.48587501888027</v>
+        <v>3.485875018880268</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-8.873929493886003</v>
+        <v>-8.679439898920018</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.3853113741106955</v>
+        <v>-0.3075155361243018</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.180685149376102</v>
+        <v>-2.140349913723985</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.856205758131792</v>
+        <v>1.880406899523062</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234395</v>
+        <v>3.480688917234394</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.161733338423241</v>
+        <v>-8.967243743457256</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.5071051026995672</v>
+        <v>-0.4293092647131735</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.46848899391334</v>
+        <v>-2.428153758261223</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.676851260635473</v>
+        <v>1.701052402026743</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860585</v>
+        <v>3.493712438860583</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.391557785587066</v>
+        <v>-9.197068190621081</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.5979190917265411</v>
+        <v>-0.520123253740147</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.631136530983501</v>
+        <v>-2.590801295331384</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.580378528231933</v>
+        <v>1.604579669623203</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767398</v>
+        <v>3.492098065767396</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.623586705323328</v>
+        <v>-9.429097110357343</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.688036930991931</v>
+        <v>-0.6102410930055373</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.693149228171924</v>
+        <v>-2.652813992519807</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.545864638547993</v>
+        <v>1.570065779939264</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792543</v>
+        <v>3.573670449792541</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.571571191354515</v>
+        <v>-9.37708159638853</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.663240389718005</v>
+        <v>-0.5854445517316109</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.693149228171924</v>
+        <v>-2.652813992519807</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.549854974234394</v>
+        <v>1.574056115625664</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628921</v>
+        <v>3.600034689628918</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.713243033078635</v>
+        <v>-9.51875343811265</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.7213843533063948</v>
+        <v>-0.6435885153200007</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.693149228171924</v>
+        <v>-2.652813992519807</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.548379747335653</v>
+        <v>1.572580888726923</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410719</v>
+        <v>3.691568158410716</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.804671114179751</v>
+        <v>-9.617660178571926</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.7429021755819689</v>
+        <v>-0.6680978013388388</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.784577309273039</v>
+        <v>-2.751720732979082</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.508576308839856</v>
+        <v>1.52829025461623</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240578</v>
+        <v>3.676837974240576</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.605519006942652</v>
+        <v>-9.418508071334827</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.6762924663338121</v>
+        <v>-0.601488092090682</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.619254783323226</v>
+        <v>-2.586398207029269</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.594718690763061</v>
+        <v>1.614432636539435</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085281</v>
+        <v>3.685157806085279</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-9.379673854223242</v>
+        <v>-9.192662918615415</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.5763753322098393</v>
+        <v>-0.5015709579667087</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.577328107736062</v>
+        <v>-2.544471531442105</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.629453769151568</v>
+        <v>1.649167714927942</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282102</v>
+        <v>3.6848402482821</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-9.093399041900547</v>
+        <v>-8.90638810629272</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.4607262627247026</v>
+        <v>-0.3859218884815721</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.577328107736062</v>
+        <v>-2.544471531442105</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.630592913707626</v>
+        <v>1.650306859484001</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116217</v>
+        <v>3.710931958116216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.866603214827213</v>
+        <v>-8.679592279219387</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.3673741577332614</v>
+        <v>-0.2925697834901309</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.509214163114518</v>
+        <v>-2.476357586820561</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.674095054642661</v>
+        <v>1.693809000419035</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.76894809908157</v>
+        <v>3.768948099081569</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.582694483898464</v>
+        <v>-8.395683548290638</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.2480769611231253</v>
+        <v>-0.1732725868799947</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.509214163114518</v>
+        <v>-2.476357586820561</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.679828758881297</v>
+        <v>1.699542704657672</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.72857435442533</v>
+        <v>3.728574354425329</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.335707233705513</v>
+        <v>-8.148696298097686</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.1590193234398098</v>
+        <v>-0.08421494919667927</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.262226912921566</v>
+        <v>-2.229370336627609</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.818283846603203</v>
+        <v>1.837997792379578</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702415</v>
+        <v>3.747699084702414</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.071870366501443</v>
+        <v>-7.884859430893617</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.06336805787108979</v>
+        <v>0.01143631637204079</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.262226912921566</v>
+        <v>-2.229370336627609</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.808400365290296</v>
+        <v>1.82811431106667</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.76631350390623</v>
+        <v>3.766313503906229</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-7.804628565633046</v>
+        <v>-7.617617630025221</v>
       </c>
       <c r="E1896" t="n">
-        <v>0.04169410197689549</v>
+        <v>0.1164984762200256</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.262226912921566</v>
+        <v>-2.229370336627609</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.806565804790922</v>
+        <v>1.826279750567296</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.78468094578195</v>
+        <v>3.784680945781949</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-7.528819402232562</v>
+        <v>-7.341808466624737</v>
       </c>
       <c r="E1897" t="n">
-        <v>0.151717452363628</v>
+        <v>0.2265218266067586</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.173207604642832</v>
+        <v>-2.140351028348875</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.859677074784701</v>
+        <v>1.879391020561076</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567246</v>
+        <v>3.800825778567244</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-7.259751814465583</v>
+        <v>-7.072740878857757</v>
       </c>
       <c r="E1898" t="n">
-        <v>0.2600129936159137</v>
+        <v>0.3348173678590438</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.904140016875853</v>
+        <v>-1.871283440581896</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.021786133590382</v>
+        <v>2.041500079366757</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487775</v>
+        <v>3.789307536487773</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-6.995691876142787</v>
+        <v>-6.808680940534961</v>
       </c>
       <c r="E1899" t="n">
-        <v>0.3523766527832799</v>
+        <v>0.42718102702641</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.640080078553057</v>
+        <v>-1.6072235022591</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.166961780422308</v>
+        <v>2.186675726198682</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309729</v>
+        <v>3.833249172309727</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-6.288612252637948</v>
+        <v>-6.101601317030123</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.6324214685249143</v>
+        <v>0.7072258427680445</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.640080078553057</v>
+        <v>-1.6072235022591</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.164174746762007</v>
+        <v>2.183888692538381</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858731</v>
+        <v>3.839370871858729</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-6.038971222651996</v>
+        <v>-5.851960287044171</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.7326215044071365</v>
+        <v>0.8074258786502666</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.390439048567105</v>
+        <v>-1.357582472273148</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.314302988641419</v>
+        <v>2.334016934417794</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096477</v>
+        <v>3.856158176096475</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-5.784429323310921</v>
+        <v>-5.597418387703096</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.833805085364324</v>
+        <v>0.9086094596074537</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.13589714922603</v>
+        <v>-1.103040572932072</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.466394949466822</v>
+        <v>2.486108895243196</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761808</v>
+        <v>3.787326853761806</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-5.550948101081322</v>
+        <v>-5.363937165473497</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.9351220030940155</v>
+        <v>1.009926377337146</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.9024159269964311</v>
+        <v>-0.8695593507024739</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.614408111642433</v>
+        <v>2.634122057418808</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255785</v>
+        <v>3.801633547255783</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-5.371239570937449</v>
+        <v>-5.184228635329625</v>
       </c>
       <c r="E1904" t="n">
-        <v>1.004113204838605</v>
+        <v>1.078917579081736</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.845244422833735</v>
+        <v>-0.8123878465397778</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.645818803827092</v>
+        <v>2.665532749603466</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860427</v>
+        <v>3.763178672860425</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-5.238964097306563</v>
+        <v>-5.051953161698738</v>
       </c>
       <c r="E1905" t="n">
-        <v>1.052390881037987</v>
+        <v>1.127195255281117</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.7129689492028484</v>
+        <v>-0.6801123729088911</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.720551574752651</v>
+        <v>2.740265520529025</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575953</v>
+        <v>3.784715218575951</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-5.04836442263341</v>
+        <v>-4.861353487025585</v>
       </c>
       <c r="E1906" t="n">
-        <v>1.131445811594885</v>
+        <v>1.206250185838015</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.5223692745296955</v>
+        <v>-0.4895126982357383</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.837726440244179</v>
+        <v>2.857440386020554</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430988</v>
+        <v>3.753878996430986</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-4.799364623949829</v>
+        <v>-4.612353688342004</v>
       </c>
       <c r="E1907" t="n">
-        <v>1.243952072291976</v>
+        <v>1.318756446535106</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.5223692745296955</v>
+        <v>-0.4895126982357383</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.850632781467838</v>
+        <v>2.870346727244212</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077646</v>
+        <v>3.692928280077644</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-4.904954613722934</v>
+        <v>-4.717943678115109</v>
       </c>
       <c r="E1908" t="n">
-        <v>1.073740146783515</v>
+        <v>1.148544521026645</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.6279592643027998</v>
+        <v>-0.5951026880088426</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.659302858004757</v>
+        <v>2.679016803781131</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457904</v>
+        <v>3.770419008457901</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-4.625927318067307</v>
+        <v>-4.438916382459482</v>
       </c>
       <c r="E1909" t="n">
-        <v>1.233895406922853</v>
+        <v>1.308699781165983</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.6279592643027998</v>
+        <v>-0.5951026880088426</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.707847199881843</v>
+        <v>2.727561145658217</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.76033011118081</v>
+        <v>3.760330111180807</v>
       </c>
       <c r="C1910" t="n">
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-4.349189143396494</v>
+        <v>-4.162178207788669</v>
       </c>
       <c r="E1910" t="n">
-        <v>1.347969688777173</v>
+        <v>1.422774063020303</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.446142603192874</v>
+        <v>-0.4132860268989168</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.820316208533793</v>
+        <v>2.840030154310167</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879203</v>
+        <v>3.723562653879201</v>
       </c>
       <c r="C1911" t="n">
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-4.222296736961423</v>
+        <v>-4.035285801353599</v>
       </c>
       <c r="E1911" t="n">
-        <v>1.390012665097722</v>
+        <v>1.464817039340852</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.3192501967578041</v>
+        <v>-0.2863936204638469</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.887737666141357</v>
+        <v>2.907451611917731</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568107</v>
+        <v>3.729966140568105</v>
       </c>
       <c r="C1912" t="n">
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-4.034709229051497</v>
+        <v>-3.847698293443672</v>
       </c>
       <c r="E1912" t="n">
-        <v>1.4580870561666</v>
+        <v>1.53289143040973</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.3192501967578041</v>
+        <v>-0.2863936204638469</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.880777054046264</v>
+        <v>2.900490999822638</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963418</v>
+        <v>3.782918957963417</v>
       </c>
       <c r="C1913" t="n">
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-3.792560835597639</v>
+        <v>-3.605549899989814</v>
       </c>
       <c r="E1913" t="n">
-        <v>1.569408767929286</v>
+        <v>1.644213142172416</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.3192501967578041</v>
+        <v>-0.2863936204638469</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.895239408427407</v>
+        <v>2.914953354203781</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192817</v>
+        <v>3.828547911192815</v>
       </c>
       <c r="C1914" t="n">
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-3.729331463829291</v>
+        <v>-3.542320528221465</v>
       </c>
       <c r="E1914" t="n">
-        <v>1.589232637095821</v>
+        <v>1.664037011338951</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.3192501967578041</v>
+        <v>-0.2863936204638469</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.889771528886602</v>
+        <v>2.909485474662976</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262047</v>
+        <v>3.828049353262045</v>
       </c>
       <c r="C1915" t="n">
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-3.542843771452285</v>
+        <v>-3.355832835844459</v>
       </c>
       <c r="E1915" t="n">
-        <v>1.6613258080572</v>
+        <v>1.73613018230033</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.1327625043807978</v>
+        <v>-0.09990592808684062</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.999162238323382</v>
+        <v>3.018876184099757</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389909</v>
+        <v>3.812450103389907</v>
       </c>
       <c r="C1916" t="n">
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-3.521694572548841</v>
+        <v>-3.334683636941016</v>
       </c>
       <c r="E1916" t="n">
-        <v>1.677486465855903</v>
+        <v>1.752290840099033</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.1116133054773545</v>
+        <v>-0.07875672918339727</v>
       </c>
       <c r="G1916" t="n">
-        <v>3.019552735902774</v>
+        <v>3.039266681679148</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788095</v>
+        <v>3.748324832788093</v>
       </c>
       <c r="C1917" t="n">
         <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-3.277929130565397</v>
+        <v>-3.090918194957571</v>
       </c>
       <c r="E1917" t="n">
-        <v>1.770773350996331</v>
+        <v>1.845577725239461</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.1116133054773545</v>
+        <v>-0.07875672918339727</v>
       </c>
       <c r="G1917" t="n">
-        <v>3.015333444249825</v>
+        <v>3.035047390026199</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527527</v>
+        <v>3.824307657527524</v>
       </c>
       <c r="C1918" t="n">
         <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-3.013901063372137</v>
+        <v>-2.826890127764311</v>
       </c>
       <c r="E1918" t="n">
-        <v>1.878508891793651</v>
+        <v>1.953313266036782</v>
       </c>
       <c r="F1918" t="n">
-        <v>0.09025209333859907</v>
+        <v>0.1231086696325563</v>
       </c>
       <c r="G1918" t="n">
-        <v>3.138576997459413</v>
+        <v>3.158290943235787</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.421894867663107</v>
+        <v>3.421894867663105</v>
       </c>
       <c r="C1919" t="n">
-        <v>2.97195201446704</v>
+        <v>3.077167816439955</v>
       </c>
       <c r="D1919" t="n">
-        <v>-2.757482876097249</v>
+        <v>-2.568437772436352</v>
       </c>
       <c r="E1919" t="n">
-        <v>1.868602439714394</v>
+        <v>2.049436283151667</v>
       </c>
       <c r="F1919" t="n">
-        <v>0.09025209333859907</v>
+        <v>0.1231086696325563</v>
       </c>
       <c r="G1919" t="n">
-        <v>3.0261032704702</v>
+        <v>3.151033018219489</v>
       </c>
     </row>
   </sheetData>
